--- a/Docs/EquipmentDesign.xlsx
+++ b/Docs/EquipmentDesign.xlsx
@@ -18,23 +18,23 @@
     <definedName name="list_Class">'Enums'!$B$2:$B$17</definedName>
     <definedName name="list_Slot">'Enums'!$C$2:$C$6</definedName>
     <definedName name="list_Bool">'Enums'!$D$2:$D$3</definedName>
-    <definedName name="list_Status">'Enums'!$E$2:$E$26</definedName>
+    <definedName name="list_Status">'Enums'!$E$2:$E$32</definedName>
     <definedName name="list_DamageCondition">'Enums'!$F$2:$F$3</definedName>
     <definedName name="list_CardTag">'Enums'!$G$2:$G$9</definedName>
     <definedName name="list_AreaKind">'Enums'!$H$2:$H$4</definedName>
     <definedName name="list_RangeShape">'Enums'!$I$2:$I$5</definedName>
     <definedName name="list_EffectTarget">'Enums'!$J$2:$J$3</definedName>
     <definedName name="list_CardKeyword">'Enums'!$K$2:$K$6</definedName>
-    <definedName name="list_EquipModType">'Enums'!$L$2:$L$12</definedName>
+    <definedName name="list_EquipModType">'Enums'!$L$2:$L$13</definedName>
     <definedName name="list_CardModType">'Enums'!$M$2:$M$9</definedName>
-    <definedName name="list_CardEffect">'Enums'!$N$2:$N$115</definedName>
-    <definedName name="list_CardData">'Enums'!$O$2:$O$148</definedName>
+    <definedName name="list_CardEffect">'Enums'!$N$2:$N$120</definedName>
+    <definedName name="list_CardData">'Enums'!$O$2:$O$155</definedName>
     <definedName name="list_EquipFolder">'Enums'!$Q$2:$Q$3</definedName>
     <definedName name="list_Buildable">'Enums'!$R$2:$R$6</definedName>
     <definedName name="list_Priority">'Enums'!$S$2:$S$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Equipment'!$A$1:$N$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Modifiers'!$A$1:$X$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Card Tuning'!$A$1:$AK$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Card Tuning'!$A$1:$AM$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Balance'!$A$1:$M$34</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="730">
   <si>
     <t>Rarity</t>
   </si>
@@ -185,888 +185,933 @@
     <t>Innate</t>
   </si>
   <si>
+    <t>AppliedStacksModifier</t>
+  </si>
+  <si>
+    <t>AreaModifier</t>
+  </si>
+  <si>
+    <t>Block 2</t>
+  </si>
+  <si>
+    <t>Aegis Totem</t>
+  </si>
+  <si>
+    <t>Rings</t>
+  </si>
+  <si>
+    <t>Needs Modifier</t>
+  </si>
+  <si>
+    <t>Med</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>Mage</t>
+  </si>
+  <si>
+    <t>Armor</t>
+  </si>
+  <si>
+    <t>DoubleNextAttack</t>
+  </si>
+  <si>
+    <t>Defence</t>
+  </si>
+  <si>
+    <t>Pattern</t>
+  </si>
+  <si>
+    <t>Manhattan</t>
+  </si>
+  <si>
+    <t>Cooldown</t>
+  </si>
+  <si>
     <t>CardTuningModifier</t>
   </si>
   <si>
-    <t>AreaModifier</t>
-  </si>
-  <si>
-    <t>Block 2</t>
-  </si>
-  <si>
-    <t>Aegis Totem</t>
-  </si>
-  <si>
-    <t>Rings</t>
-  </si>
-  <si>
-    <t>Needs Modifier</t>
-  </si>
-  <si>
-    <t>Med</t>
-  </si>
-  <si>
-    <t>Rare</t>
-  </si>
-  <si>
-    <t>Mage</t>
-  </si>
-  <si>
-    <t>Armor</t>
-  </si>
-  <si>
-    <t>DoubleNextAttack</t>
-  </si>
-  <si>
-    <t>Defence</t>
-  </si>
-  <si>
-    <t>Pattern</t>
-  </si>
-  <si>
-    <t>Manhattan</t>
-  </si>
-  <si>
-    <t>Cooldown</t>
+    <t>CostModifier</t>
+  </si>
+  <si>
+    <t>Block 3</t>
+  </si>
+  <si>
+    <t>Anvil Totem</t>
+  </si>
+  <si>
+    <t>Needs Status</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Legendary</t>
+  </si>
+  <si>
+    <t>Knight+Mage</t>
+  </si>
+  <si>
+    <t>Hat</t>
+  </si>
+  <si>
+    <t>Poison</t>
+  </si>
+  <si>
+    <t>Movement</t>
+  </si>
+  <si>
+    <t>SelfTile</t>
+  </si>
+  <si>
+    <t>Dormant</t>
   </si>
   <si>
     <t>ConditionalDamageModifier</t>
   </si>
   <si>
-    <t>CostModifier</t>
-  </si>
-  <si>
-    <t>Block 3</t>
-  </si>
-  <si>
-    <t>Anvil Totem</t>
-  </si>
-  <si>
-    <t>Needs Status</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Legendary</t>
-  </si>
-  <si>
-    <t>Knight+Mage</t>
-  </si>
-  <si>
-    <t>Hat</t>
-  </si>
-  <si>
-    <t>Poison</t>
-  </si>
-  <si>
-    <t>Movement</t>
-  </si>
-  <si>
-    <t>SelfTile</t>
-  </si>
-  <si>
-    <t>Dormant</t>
+    <t>EffectSwapModifier</t>
+  </si>
+  <si>
+    <t>Block 4</t>
+  </si>
+  <si>
+    <t>ArcaneLance</t>
+  </si>
+  <si>
+    <t>Needs Hook</t>
+  </si>
+  <si>
+    <t>NotOffered</t>
+  </si>
+  <si>
+    <t>Rogue</t>
+  </si>
+  <si>
+    <t>Boots</t>
+  </si>
+  <si>
+    <t>Frozen</t>
+  </si>
+  <si>
+    <t>Rebound</t>
   </si>
   <si>
     <t>DamageBonusModifier</t>
   </si>
   <si>
-    <t>EffectSwapModifier</t>
-  </si>
-  <si>
-    <t>Block 4</t>
-  </si>
-  <si>
-    <t>ArcaneLance</t>
-  </si>
-  <si>
-    <t>Needs Hook</t>
-  </si>
-  <si>
-    <t>NotOffered</t>
-  </si>
-  <si>
-    <t>Rogue</t>
-  </si>
-  <si>
-    <t>Boots</t>
-  </si>
-  <si>
-    <t>Frozen</t>
-  </si>
-  <si>
-    <t>Rebound</t>
+    <t>KeywordModifier</t>
+  </si>
+  <si>
+    <t>Cleanse Poison Heal</t>
+  </si>
+  <si>
+    <t>Attack and Block</t>
+  </si>
+  <si>
+    <t>Needs System</t>
+  </si>
+  <si>
+    <t>Knight+Rogue</t>
+  </si>
+  <si>
+    <t>Shield</t>
+  </si>
+  <si>
+    <t>Fire</t>
   </si>
   <si>
     <t>GrantBonusModifier</t>
   </si>
   <si>
-    <t>KeywordModifier</t>
-  </si>
-  <si>
-    <t>Cleanse Poison Heal</t>
-  </si>
-  <si>
-    <t>Attack and Block</t>
-  </si>
-  <si>
-    <t>Needs System</t>
-  </si>
-  <si>
-    <t>Knight+Rogue</t>
-  </si>
-  <si>
-    <t>Shield</t>
-  </si>
-  <si>
-    <t>Fire</t>
+    <t>MagnitudeModifier</t>
+  </si>
+  <si>
+    <t>Cone3</t>
+  </si>
+  <si>
+    <t>Backstab</t>
+  </si>
+  <si>
+    <t>Mage+Rogue</t>
+  </si>
+  <si>
+    <t>Block</t>
+  </si>
+  <si>
+    <t>Summon</t>
   </si>
   <si>
     <t>KillRewardModifier</t>
   </si>
   <si>
-    <t>MagnitudeModifier</t>
-  </si>
-  <si>
-    <t>Cone3</t>
-  </si>
-  <si>
-    <t>Backstab</t>
-  </si>
-  <si>
-    <t>Mage+Rogue</t>
-  </si>
-  <si>
-    <t>Block</t>
-  </si>
-  <si>
-    <t>Summon</t>
+    <t>RangeModifier</t>
+  </si>
+  <si>
+    <t>Damage 1</t>
+  </si>
+  <si>
+    <t>Bastion Totem</t>
+  </si>
+  <si>
+    <t>Knight+Mage+Rogue</t>
+  </si>
+  <si>
+    <t>Parry</t>
+  </si>
+  <si>
+    <t>Healing</t>
   </si>
   <si>
     <t>ResourceModifier</t>
   </si>
   <si>
-    <t>RangeModifier</t>
+    <t>RemoveEntryModifier</t>
+  </si>
+  <si>
+    <t>Damage 12</t>
+  </si>
+  <si>
+    <t>Beacon Totem</t>
+  </si>
+  <si>
+    <t>Cleric</t>
+  </si>
+  <si>
+    <t>Rooted</t>
+  </si>
+  <si>
+    <t>ScalingDamageModifier</t>
   </si>
   <si>
     <t>Damage 2</t>
   </si>
   <si>
-    <t>Bastion Totem</t>
-  </si>
-  <si>
-    <t>Knight+Mage+Rogue</t>
-  </si>
-  <si>
-    <t>Parry</t>
-  </si>
-  <si>
-    <t>Healing</t>
-  </si>
-  <si>
-    <t>ScalingDamageModifier</t>
-  </si>
-  <si>
-    <t>RemoveEntryModifier</t>
+    <t>Binding Totem</t>
+  </si>
+  <si>
+    <t>Knight+Cleric</t>
+  </si>
+  <si>
+    <t>DoubleShield</t>
+  </si>
+  <si>
+    <t>StatusGrantModifier</t>
   </si>
   <si>
     <t>Damage 3</t>
   </si>
   <si>
-    <t>Beacon Totem</t>
-  </si>
-  <si>
-    <t>Cleric</t>
-  </si>
-  <si>
-    <t>Rooted</t>
-  </si>
-  <si>
-    <t>StatusGrantModifier</t>
+    <t>Bite</t>
+  </si>
+  <si>
+    <t>Mage+Cleric</t>
+  </si>
+  <si>
+    <t>Dodge</t>
+  </si>
+  <si>
+    <t>SummonHealthModifier</t>
   </si>
   <si>
     <t>Damage 4</t>
   </si>
   <si>
-    <t>Binding Totem</t>
-  </si>
-  <si>
-    <t>Knight+Cleric</t>
-  </si>
-  <si>
-    <t>DoubleShield</t>
-  </si>
-  <si>
-    <t>SummonHealthModifier</t>
+    <t>BlackGuard</t>
+  </si>
+  <si>
+    <t>Knight+Mage+Cleric</t>
+  </si>
+  <si>
+    <t>Weaken</t>
+  </si>
+  <si>
+    <t>ThornsModifier</t>
   </si>
   <si>
     <t>Damage 5</t>
   </si>
   <si>
-    <t>BlackGuard</t>
-  </si>
-  <si>
-    <t>Mage+Cleric</t>
-  </si>
-  <si>
-    <t>Dodge</t>
-  </si>
-  <si>
-    <t>ThornsModifier</t>
+    <t>Blade Ward</t>
+  </si>
+  <si>
+    <t>Rogue+Cleric</t>
+  </si>
+  <si>
+    <t>Taunt</t>
   </si>
   <si>
     <t>Damage 6</t>
   </si>
   <si>
-    <t>Blade Ward</t>
-  </si>
-  <si>
-    <t>Knight+Mage+Cleric</t>
-  </si>
-  <si>
-    <t>Weaken</t>
+    <t>Knight+Rogue+Cleric</t>
+  </si>
+  <si>
+    <t>Summoned</t>
   </si>
   <si>
     <t>Damage 7</t>
   </si>
   <si>
-    <t>Rogue+Cleric</t>
-  </si>
-  <si>
-    <t>Taunt</t>
+    <t>Bloodied Resolve</t>
+  </si>
+  <si>
+    <t>Mage+Rogue+Cleric</t>
+  </si>
+  <si>
+    <t>PoisonBlade</t>
   </si>
   <si>
     <t>Damage 8</t>
   </si>
   <si>
-    <t>Bloodied Resolve</t>
-  </si>
-  <si>
-    <t>Knight+Rogue+Cleric</t>
-  </si>
-  <si>
-    <t>Summoned</t>
+    <t>Bloodmoon Totem</t>
+  </si>
+  <si>
+    <t>Knight+Mage+Rogue+Cleric</t>
+  </si>
+  <si>
+    <t>Stealth</t>
   </si>
   <si>
     <t>Damage 9</t>
   </si>
   <si>
-    <t>Bloodmoon Totem</t>
-  </si>
-  <si>
-    <t>Mage+Rogue+Cleric</t>
-  </si>
-  <si>
-    <t>PoisonBlade</t>
+    <t>Bloodpact Totem</t>
+  </si>
+  <si>
+    <t>Vulnerable</t>
   </si>
   <si>
     <t>Discard 1</t>
   </si>
   <si>
-    <t>Bloodpact Totem</t>
-  </si>
-  <si>
-    <t>Knight+Mage+Rogue+Cleric</t>
-  </si>
-  <si>
-    <t>Stealth</t>
-  </si>
-  <si>
     <t>Bloom Totem</t>
   </si>
   <si>
-    <t>Vulnerable</t>
+    <t>GainMultiplier</t>
+  </si>
+  <si>
+    <t>BoneBulwark</t>
+  </si>
+  <si>
+    <t>Potency</t>
   </si>
   <si>
     <t>Double Next Attack</t>
   </si>
   <si>
-    <t>BoneBulwark</t>
-  </si>
-  <si>
-    <t>GainMultiplier</t>
+    <t>BoneChill</t>
+  </si>
+  <si>
+    <t>TurnTick</t>
   </si>
   <si>
     <t>Double Shield</t>
   </si>
   <si>
-    <t>BoneChill</t>
-  </si>
-  <si>
-    <t>Potency</t>
+    <t>BoulderSmash</t>
+  </si>
+  <si>
+    <t>Regeneration</t>
   </si>
   <si>
     <t>Draw 1</t>
   </si>
   <si>
-    <t>BoulderSmash</t>
-  </si>
-  <si>
-    <t>TurnTick</t>
+    <t>Buff</t>
+  </si>
+  <si>
+    <t>Lifesteal</t>
   </si>
   <si>
     <t>Energy 1</t>
   </si>
   <si>
-    <t>Buff</t>
-  </si>
-  <si>
-    <t>Regeneration</t>
+    <t>Bulwark Totem</t>
+  </si>
+  <si>
+    <t>FlatDamageDealt</t>
   </si>
   <si>
     <t>Energy 3</t>
   </si>
   <si>
-    <t>Bulwark Totem</t>
-  </si>
-  <si>
-    <t>Lifesteal</t>
+    <t>CallTheDamned</t>
+  </si>
+  <si>
+    <t>FlatDamageTaken</t>
   </si>
   <si>
     <t>Freeze</t>
   </si>
   <si>
-    <t>CallReinforcements</t>
-  </si>
-  <si>
-    <t>FlatDamageDealt</t>
+    <t>CallTheSwarm</t>
+  </si>
+  <si>
+    <t>GainBonus</t>
   </si>
   <si>
     <t>Heal 10</t>
   </si>
   <si>
-    <t>CallTheDamned</t>
-  </si>
-  <si>
-    <t>FlatDamageTaken</t>
+    <t>Chaos Totem</t>
+  </si>
+  <si>
+    <t>Warded</t>
   </si>
   <si>
     <t>Heal 3</t>
   </si>
   <si>
-    <t>CallTheSwarm</t>
-  </si>
-  <si>
-    <t>GainBonus</t>
+    <t>Chomp</t>
+  </si>
+  <si>
+    <t>Thorns</t>
   </si>
   <si>
     <t>Heal 5</t>
   </si>
   <si>
-    <t>Chaos Totem</t>
+    <t>ClawAttack</t>
+  </si>
+  <si>
+    <t>Splitting</t>
   </si>
   <si>
     <t>Heal 9</t>
   </si>
   <si>
-    <t>Chomp</t>
+    <t>Cleansing Light</t>
+  </si>
+  <si>
+    <t>Escaping</t>
   </si>
   <si>
     <t>Lifesteal 1</t>
   </si>
   <si>
-    <t>Cleansing Light</t>
+    <t>Cleave</t>
+  </si>
+  <si>
+    <t>Pilfered</t>
   </si>
   <si>
     <t>Move</t>
   </si>
   <si>
-    <t>Cleave</t>
+    <t>Conduit Totem</t>
+  </si>
+  <si>
+    <t>Sapped</t>
   </si>
   <si>
     <t>Parry 1</t>
   </si>
   <si>
-    <t>Conduit Totem</t>
-  </si>
-  <si>
     <t>ConjureOoze</t>
   </si>
   <si>
+    <t>Pilfered 1</t>
+  </si>
+  <si>
+    <t>Contagion Totem</t>
+  </si>
+  <si>
+    <t>Cure Wounds</t>
+  </si>
+  <si>
     <t>Poison 2</t>
   </si>
   <si>
-    <t>Contagion Totem</t>
+    <t>Curse Totem</t>
   </si>
   <si>
     <t>Poison 3</t>
   </si>
   <si>
-    <t>Cure Wounds</t>
+    <t>DarkBolt</t>
   </si>
   <si>
     <t>Poison 4</t>
   </si>
   <si>
-    <t>Curse Totem</t>
+    <t>DeathsToll</t>
   </si>
   <si>
     <t>Poison Blade 3</t>
   </si>
   <si>
-    <t>DarkBolt</t>
+    <t>Decoy Totem</t>
   </si>
   <si>
     <t>Purge Poison</t>
   </si>
   <si>
-    <t>DeathsToll</t>
-  </si>
-  <si>
     <t>Push</t>
   </si>
   <si>
-    <t>Decoy Totem</t>
+    <t>DreadCleave</t>
   </si>
   <si>
     <t>Regeneration 4</t>
   </si>
   <si>
+    <t>Dull Blade</t>
+  </si>
+  <si>
     <t>Root</t>
   </si>
   <si>
-    <t>DrainBite</t>
+    <t>Echo Totem</t>
+  </si>
+  <si>
+    <t>Sapped 2</t>
+  </si>
+  <si>
+    <t>EmberShroud</t>
   </si>
   <si>
     <t>Self Damage 5</t>
   </si>
   <si>
-    <t>DreadCleave</t>
+    <t>EnemyArrow</t>
   </si>
   <si>
     <t>Shield 10</t>
   </si>
   <si>
-    <t>Dull Blade</t>
+    <t>EnemySlash</t>
   </si>
   <si>
     <t>Shield 3</t>
   </si>
   <si>
-    <t>Echo Totem</t>
+    <t>Enfeeble Totem</t>
+  </si>
+  <si>
+    <t>Shield 4</t>
+  </si>
+  <si>
+    <t>Engulf</t>
   </si>
   <si>
     <t>Shield 5</t>
   </si>
   <si>
-    <t>EmberShroud</t>
+    <t>Entangle</t>
   </si>
   <si>
     <t>Shield 7</t>
   </si>
   <si>
-    <t>EnemyArrow</t>
+    <t>Evasion</t>
   </si>
   <si>
     <t>Stealth 2</t>
   </si>
   <si>
-    <t>EnemySlash</t>
+    <t>ExecutionersBlow</t>
   </si>
   <si>
     <t>Strength 1</t>
   </si>
   <si>
-    <t>Enfeeble Totem</t>
+    <t>Fireball</t>
   </si>
   <si>
     <t>Strength 3</t>
   </si>
   <si>
-    <t>Engulf</t>
+    <t>Firebolt</t>
   </si>
   <si>
     <t>SummonAegisTotem</t>
   </si>
   <si>
-    <t>Entangle</t>
+    <t>Flame Cone</t>
   </si>
   <si>
     <t>SummonAnvilTotem</t>
   </si>
   <si>
-    <t>Evasion</t>
+    <t>Foresight</t>
   </si>
   <si>
     <t>SummonBastionTotem</t>
   </si>
   <si>
-    <t>ExecutionersBlow</t>
+    <t>Fortune Totem</t>
   </si>
   <si>
     <t>SummonBatMinion</t>
   </si>
   <si>
-    <t>Fireball</t>
+    <t>Fracture Totem</t>
   </si>
   <si>
     <t>SummonBeaconTotem</t>
   </si>
   <si>
-    <t>Firebolt</t>
-  </si>
-  <si>
     <t>SummonBindingTotem</t>
   </si>
   <si>
-    <t>Flame Cone</t>
+    <t>Fury Totem</t>
   </si>
   <si>
     <t>SummonBloodmoonTotem</t>
   </si>
   <si>
-    <t>Foresight</t>
+    <t>Ghoststep Totem</t>
   </si>
   <si>
     <t>SummonBloodpactTotem</t>
   </si>
   <si>
-    <t>Fortune Totem</t>
+    <t>Gnaw</t>
   </si>
   <si>
     <t>SummonBloomTotem</t>
   </si>
   <si>
-    <t>Fracture Totem</t>
+    <t>GraveTithe</t>
   </si>
   <si>
     <t>SummonBulwarkTotem</t>
   </si>
   <si>
+    <t>Guardian's Aegis</t>
+  </si>
+  <si>
     <t>SummonChaosTotem</t>
   </si>
   <si>
-    <t>Fury Totem</t>
+    <t>Heal Totem</t>
   </si>
   <si>
     <t>SummonConduitTotem</t>
   </si>
   <si>
-    <t>Ghoststep Totem</t>
+    <t>Heal Word</t>
   </si>
   <si>
     <t>SummonContagionTotem</t>
   </si>
   <si>
-    <t>Gnaw</t>
+    <t>HeavySwing</t>
   </si>
   <si>
     <t>SummonCurseTotem</t>
   </si>
   <si>
-    <t>Guardian's Aegis</t>
+    <t>Hex Totem</t>
   </si>
   <si>
     <t>SummonDecoyTotem</t>
   </si>
   <si>
-    <t>Heal Totem</t>
+    <t>Ice Shard</t>
   </si>
   <si>
     <t>SummonEchoTotem</t>
   </si>
   <si>
-    <t>Heal Word</t>
+    <t>Leech Totem</t>
   </si>
   <si>
     <t>SummonEnfeebleTotem</t>
   </si>
   <si>
-    <t>HeavySwing</t>
+    <t>LifeLeech</t>
   </si>
   <si>
     <t>SummonFortuneTotem</t>
   </si>
   <si>
-    <t>Hex Totem</t>
+    <t>Lodestone Totem</t>
   </si>
   <si>
     <t>SummonFractureTotem</t>
   </si>
   <si>
-    <t>Ice Shard</t>
+    <t>Mend and Fortify</t>
   </si>
   <si>
     <t>SummonFuryTotem</t>
   </si>
   <si>
-    <t>Leech Totem</t>
+    <t>Mend and Guard</t>
   </si>
   <si>
     <t>SummonGhoststepTotem</t>
   </si>
   <si>
-    <t>LifeLeech</t>
+    <t>MeteorFall</t>
   </si>
   <si>
     <t>SummonGoblinMinion</t>
   </si>
   <si>
-    <t>Lodestone Totem</t>
+    <t>Momentum Totem</t>
   </si>
   <si>
     <t>SummonHealTotem</t>
   </si>
   <si>
-    <t>Mend and Fortify</t>
-  </si>
-  <si>
     <t>SummonHeavyBanditMinion</t>
   </si>
   <si>
-    <t>Mend and Guard</t>
+    <t>MoveInnate</t>
   </si>
   <si>
     <t>SummonHexTotem</t>
   </si>
   <si>
-    <t>MeteorFall</t>
+    <t>MoveInnate2</t>
   </si>
   <si>
     <t>SummonLeechTotem</t>
   </si>
   <si>
-    <t>Momentum Totem</t>
+    <t>Overflow</t>
   </si>
   <si>
     <t>SummonLightBanditMinion</t>
   </si>
   <si>
+    <t>Panache</t>
+  </si>
+  <si>
     <t>SummonLodestoneTotem</t>
   </si>
   <si>
-    <t>MoveInnate</t>
-  </si>
-  <si>
     <t>SummonMomentumTotem</t>
   </si>
   <si>
-    <t>Overflow</t>
+    <t>PlagueBite</t>
   </si>
   <si>
     <t>SummonPebbleMinion</t>
   </si>
   <si>
-    <t>Panache</t>
+    <t>Poison Blade</t>
   </si>
   <si>
     <t>SummonRallyTotem</t>
   </si>
   <si>
+    <t>Poison Dagger</t>
+  </si>
+  <si>
     <t>SummonRampartTotem</t>
   </si>
   <si>
-    <t>PincerGrip</t>
+    <t>Poison Dart</t>
   </si>
   <si>
     <t>SummonReinforceTotem</t>
   </si>
   <si>
-    <t>PlagueBite</t>
+    <t>Purge</t>
   </si>
   <si>
     <t>SummonRotTotem</t>
   </si>
   <si>
-    <t>Poison Blade</t>
+    <t>Quick Attack</t>
   </si>
   <si>
     <t>SummonRuinTotem</t>
   </si>
   <si>
-    <t>Poison Dagger</t>
+    <t>QuickCut</t>
   </si>
   <si>
     <t>SummonSanctuaryTotem</t>
   </si>
   <si>
-    <t>Poison Dart</t>
+    <t>RaiseDead</t>
   </si>
   <si>
     <t>SummonSapTotem</t>
   </si>
   <si>
-    <t>Purge</t>
+    <t>Rally</t>
   </si>
   <si>
     <t>SummonScholarTotem</t>
   </si>
   <si>
-    <t>Quick Attack</t>
+    <t>Rally Totem</t>
   </si>
   <si>
     <t>SummonSentinelTotem</t>
   </si>
   <si>
-    <t>QuickCut</t>
+    <t>Rampart Totem</t>
   </si>
   <si>
     <t>SummonShackleTotem</t>
   </si>
   <si>
-    <t>RaiseDead</t>
+    <t>Reinforce Totem</t>
   </si>
   <si>
     <t>SummonSkeletonAlly</t>
   </si>
   <si>
-    <t>Rally</t>
+    <t>Renew</t>
   </si>
   <si>
     <t>SummonSkeletonMinion</t>
   </si>
   <si>
-    <t>Rally Totem</t>
+    <t>Renewing Touch</t>
   </si>
   <si>
     <t>SummonSkeletonWarrior</t>
   </si>
   <si>
-    <t>Rampart Totem</t>
+    <t>Riposte</t>
   </si>
   <si>
     <t>SummonSlimeMinion</t>
   </si>
   <si>
-    <t>Reinforce Totem</t>
+    <t>Roll</t>
   </si>
   <si>
     <t>SummonSpikeTotem</t>
   </si>
   <si>
-    <t>Renew</t>
+    <t>Rot Totem</t>
   </si>
   <si>
     <t>SummonThornwoodTotem</t>
   </si>
   <si>
-    <t>Renewing Touch</t>
+    <t>RoyalCommand</t>
   </si>
   <si>
     <t>SummonTotem</t>
   </si>
   <si>
-    <t>Riposte</t>
+    <t>RoyalGuard</t>
   </si>
   <si>
     <t>SummonTowerTotem</t>
   </si>
   <si>
-    <t>Roll</t>
-  </si>
-  <si>
-    <t>SummonTutorialSkeleton</t>
-  </si>
-  <si>
-    <t>Rot Totem</t>
+    <t>Ruin Totem</t>
   </si>
   <si>
     <t>SummonTwinTotem</t>
   </si>
   <si>
-    <t>RoyalCommand</t>
+    <t>Rust Armor</t>
   </si>
   <si>
     <t>SummonVeilTotem</t>
   </si>
   <si>
-    <t>RoyalGuard</t>
+    <t>Sanctuary Totem</t>
   </si>
   <si>
     <t>SummonVenombladeTotem</t>
   </si>
   <si>
-    <t>Ruin Totem</t>
+    <t>Sap Totem</t>
   </si>
   <si>
     <t>SummonVenomTotem</t>
   </si>
   <si>
-    <t>Rust Armor</t>
+    <t>Scholar Totem</t>
   </si>
   <si>
     <t>SummonWarcryTotem</t>
   </si>
   <si>
-    <t>Sanctuary Totem</t>
+    <t>Second Wind</t>
   </si>
   <si>
     <t>SummonWarlordTotem</t>
   </si>
   <si>
-    <t>Sap Totem</t>
+    <t>SeismicSlam</t>
   </si>
   <si>
     <t>SummonWellheadTotem</t>
   </si>
   <si>
-    <t>Scholar Totem</t>
+    <t>Sentinel Totem</t>
   </si>
   <si>
     <t>SummonWellspringTotem</t>
   </si>
   <si>
-    <t>Second Wind</t>
+    <t>Shackle Totem</t>
   </si>
   <si>
     <t>SummonWhetstoneTotem</t>
   </si>
   <si>
-    <t>SeismicSlam</t>
+    <t>ShadowWard</t>
   </si>
   <si>
     <t>Swap</t>
   </si>
   <si>
-    <t>Sentinel Totem</t>
-  </si>
-  <si>
-    <t>Shackle Totem</t>
-  </si>
-  <si>
-    <t>ShadowWard</t>
+    <t>Shambles</t>
+  </si>
+  <si>
+    <t>Thorns 3</t>
+  </si>
+  <si>
+    <t>Shield Totem</t>
+  </si>
+  <si>
+    <t>ShieldBash</t>
   </si>
   <si>
     <t>Vulnerable 2</t>
   </si>
   <si>
-    <t>Shambles</t>
+    <t>Slash</t>
   </si>
   <si>
     <t>Wall of Flames</t>
   </si>
   <si>
+    <t>Slash+</t>
+  </si>
+  <si>
     <t>Wall of Force</t>
   </si>
   <si>
-    <t>Shield Totem</t>
+    <t>Smite</t>
   </si>
   <si>
     <t>Wall3</t>
   </si>
   <si>
-    <t>ShieldBash</t>
-  </si>
-  <si>
-    <t>Slash</t>
+    <t>SoulDrain</t>
+  </si>
+  <si>
+    <t>SoulReap</t>
   </si>
   <si>
     <t>Weaken 2</t>
   </si>
   <si>
-    <t>Slash+</t>
+    <t>SoulSwap</t>
   </si>
   <si>
     <t>X-Pattern</t>
   </si>
   <si>
-    <t>Smite</t>
-  </si>
-  <si>
-    <t>SoulReap</t>
-  </si>
-  <si>
     <t>Spike Totem</t>
   </si>
   <si>
@@ -1088,9 +1133,15 @@
     <t>Strengthen</t>
   </si>
   <si>
+    <t>SummonDrawTotem</t>
+  </si>
+  <si>
     <t>SummonImp</t>
   </si>
   <si>
+    <t>SummonPebble</t>
+  </si>
+  <si>
     <t>SummonSkeleton</t>
   </si>
   <si>
@@ -1100,6 +1151,9 @@
     <t>Teleport</t>
   </si>
   <si>
+    <t>TeleportInnate</t>
+  </si>
+  <si>
     <t>Thornwood Totem</t>
   </si>
   <si>
@@ -1121,6 +1175,9 @@
     <t>Venomblade Totem</t>
   </si>
   <si>
+    <t>VenomCut</t>
+  </si>
+  <si>
     <t>VoidBarrier</t>
   </si>
   <si>
@@ -1202,7 +1259,7 @@
     <t>Fire Mage's Hat</t>
   </si>
   <si>
-    <t>Fire cards gain a 3x3 splash.</t>
+    <t>Firebolt gains a 3x3 splash.</t>
   </si>
   <si>
     <t>Area: Chebyshev 0-1</t>
@@ -1253,7 +1310,7 @@
     <t>Totem Anchor</t>
   </si>
   <si>
-    <t>Totems you summon have +7 max health.</t>
+    <t>Totems you summon have +10 max health.</t>
   </si>
   <si>
     <t>Totems: +10 max health</t>
@@ -1412,7 +1469,7 @@
     <t>Glacier Band</t>
   </si>
   <si>
-    <t>Permanently under the effect of Shield 2.</t>
+    <t>Permanent Shield: -2 damage from every hit taken.</t>
   </si>
   <si>
     <t>Permanent Shield 2</t>
@@ -1481,7 +1538,7 @@
     <t>Rimeguard Band</t>
   </si>
   <si>
-    <t>Permanently under the effect of Block 2.</t>
+    <t>Permanent Block: -3 damage from every hit taken.</t>
   </si>
   <si>
     <t>Permanent Block 2</t>
@@ -1505,7 +1562,7 @@
     <t>Seraph's Ward</t>
   </si>
   <si>
-    <t>Permanently under the effect of Shield 3, and +1 Shield whenever you gain Shield.</t>
+    <t>Permanent Shield: -3 damage from every hit taken, and +1 Shield whenever you gain Shield.</t>
   </si>
   <si>
     <t>Permanent Shield 3 | Shield +1 per grant</t>
@@ -1571,7 +1628,7 @@
     <t>+1 Poison whenever you apply Poison.</t>
   </si>
   <si>
-    <t>Poison +1 per grant</t>
+    <t>Poison you apply: +1 stacks</t>
   </si>
   <si>
     <t>fd782f182f028cf4e87fd2756788cd35</t>
@@ -1763,7 +1820,7 @@
     <t>-3826258581685131776</t>
   </si>
   <si>
-    <t>-6928115594443510871</t>
+    <t>-3303880285105443153</t>
   </si>
   <si>
     <t>5556164077145046266</t>
@@ -1793,6 +1850,9 @@
     <t>area.radius.minDistance</t>
   </si>
   <si>
+    <t>area.radius.requiresRoute</t>
+  </si>
+  <si>
     <t>area.radius.shape</t>
   </si>
   <si>
@@ -1820,6 +1880,9 @@
     <t>entry.area.radius.minDistance</t>
   </si>
   <si>
+    <t>entry.area.radius.requiresRoute</t>
+  </si>
+  <si>
     <t>entry.area.radius.shape</t>
   </si>
   <si>
@@ -2003,6 +2066,9 @@
     <t>(no description authored)</t>
   </si>
   <si>
+    <t>Which status gains the extra stacks when the wearer applies it to somebody else.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  filter.tags</t>
   </si>
   <si>
@@ -2075,6 +2141,12 @@
     <t>Furthest tile that may be clicked. Ignored by Anywhere and SelfTile.</t>
   </si>
   <si>
+    <t xml:space="preserve">  entry.area.radius.requiresRoute</t>
+  </si>
+  <si>
+    <t>Movement only: the target must be reachable by walking within Max Distance steps, so a Wall of Force blocks the way. Off for teleports and for every non-movement card.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  entry.area.pattern</t>
   </si>
   <si>
@@ -2121,6 +2193,9 @@
   </si>
   <si>
     <t xml:space="preserve">  area.radius.maxDistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  area.radius.requiresRoute</t>
   </si>
   <si>
     <t xml:space="preserve">  area.pattern</t>
@@ -2240,7 +2315,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:T148"/>
+  <dimension ref="A1:T155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -2682,1043 +2757,1114 @@
       <c r="E13" s="0" t="s">
         <v>127</v>
       </c>
+      <c r="L13" s="0" t="s">
+        <v>128</v>
+      </c>
       <c r="N13" s="0" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O13" s="0" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="0" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="N14" s="0" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="O14" s="0" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="0" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N15" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O15" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N16" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O16" s="0" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="0" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N17" s="0" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="O17" s="0" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18">
       <c r="E18" s="0" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="N18" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O18" s="0" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19">
       <c r="E19" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N19" s="0" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="O19" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20">
       <c r="E20" s="0" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N20" s="0" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O20" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21">
       <c r="E21" s="0" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N21" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O21" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22">
       <c r="E22" s="0" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N22" s="0" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O22" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23">
       <c r="E23" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N23" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O23" s="0" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24">
       <c r="E24" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N24" s="0" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O24" s="0" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25">
       <c r="E25" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N25" s="0" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O25" s="0" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26">
       <c r="E26" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N26" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O26" s="0" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27">
+      <c r="E27" s="0" t="s">
+        <v>172</v>
+      </c>
       <c r="N27" s="0" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="O27" s="0" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28">
+      <c r="E28" s="0" t="s">
+        <v>175</v>
+      </c>
       <c r="N28" s="0" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="O28" s="0" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29">
+      <c r="E29" s="0" t="s">
+        <v>178</v>
+      </c>
       <c r="N29" s="0" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="O29" s="0" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30">
+      <c r="E30" s="0" t="s">
+        <v>181</v>
+      </c>
       <c r="N30" s="0" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="O30" s="0" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="31">
+      <c r="E31" s="0" t="s">
+        <v>184</v>
+      </c>
       <c r="N31" s="0" t="s">
-        <v>71</v>
+        <v>185</v>
       </c>
       <c r="O31" s="0" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32">
+      <c r="E32" s="0" t="s">
+        <v>187</v>
+      </c>
       <c r="N32" s="0" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="O32" s="0" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="33">
       <c r="N33" s="0" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="O33" s="0" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34">
       <c r="N34" s="0" t="s">
-        <v>184</v>
+        <v>71</v>
       </c>
       <c r="O34" s="0" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35">
       <c r="N35" s="0" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="O35" s="0" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="36">
       <c r="N36" s="0" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="O36" s="0" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
     </row>
     <row r="37">
       <c r="N37" s="0" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="O37" s="0" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
     </row>
     <row r="38">
       <c r="N38" s="0" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="O38" s="0" t="s">
-        <v>122</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39">
       <c r="N39" s="0" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="O39" s="0" t="s">
-        <v>194</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40">
       <c r="N40" s="0" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="O40" s="0" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
     </row>
     <row r="41">
       <c r="N41" s="0" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="O41" s="0" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="42">
       <c r="N42" s="0" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="O42" s="0" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
     </row>
     <row r="43">
       <c r="N43" s="0" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="O43" s="0" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="44">
       <c r="N44" s="0" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="O44" s="0" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="45">
       <c r="N45" s="0" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="O45" s="0" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="46">
       <c r="N46" s="0" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="O46" s="0" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="47">
       <c r="N47" s="0" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="O47" s="0" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
     </row>
     <row r="48">
       <c r="N48" s="0" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="O48" s="0" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
     </row>
     <row r="49">
       <c r="N49" s="0" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="O49" s="0" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="50">
       <c r="N50" s="0" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="O50" s="0" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="51">
       <c r="N51" s="0" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="O51" s="0" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="52">
       <c r="N52" s="0" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="O52" s="0" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="53">
       <c r="N53" s="0" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="O53" s="0" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="54">
       <c r="N54" s="0" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="O54" s="0" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="55">
       <c r="N55" s="0" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="O55" s="0" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="56">
       <c r="N56" s="0" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="O56" s="0" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="57">
       <c r="N57" s="0" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="O57" s="0" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="58">
       <c r="N58" s="0" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="O58" s="0" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
     </row>
     <row r="59">
       <c r="N59" s="0" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="O59" s="0" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="60">
       <c r="N60" s="0" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="O60" s="0" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="61">
       <c r="N61" s="0" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="O61" s="0" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
     </row>
     <row r="62">
       <c r="N62" s="0" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="O62" s="0" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
     </row>
     <row r="63">
       <c r="N63" s="0" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="O63" s="0" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
     </row>
     <row r="64">
       <c r="N64" s="0" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="O64" s="0" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
     </row>
     <row r="65">
       <c r="N65" s="0" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="O65" s="0" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
     </row>
     <row r="66">
       <c r="N66" s="0" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="O66" s="0" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
     </row>
     <row r="67">
       <c r="N67" s="0" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="O67" s="0" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="68">
       <c r="N68" s="0" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="O68" s="0" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
     </row>
     <row r="69">
       <c r="N69" s="0" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="O69" s="0" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
     </row>
     <row r="70">
       <c r="N70" s="0" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="O70" s="0" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
     </row>
     <row r="71">
       <c r="N71" s="0" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="O71" s="0" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
     </row>
     <row r="72">
       <c r="N72" s="0" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="O72" s="0" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
     </row>
     <row r="73">
       <c r="N73" s="0" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="O73" s="0" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="74">
       <c r="N74" s="0" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="O74" s="0" t="s">
-        <v>175</v>
+        <v>270</v>
       </c>
     </row>
     <row r="75">
       <c r="N75" s="0" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="O75" s="0" t="s">
-        <v>264</v>
+        <v>185</v>
       </c>
     </row>
     <row r="76">
       <c r="N76" s="0" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="O76" s="0" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="77">
       <c r="N77" s="0" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="O77" s="0" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="78">
       <c r="N78" s="0" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="O78" s="0" t="s">
-        <v>105</v>
+        <v>277</v>
       </c>
     </row>
     <row r="79">
       <c r="N79" s="0" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="O79" s="0" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="80">
       <c r="N80" s="0" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="O80" s="0" t="s">
-        <v>273</v>
+        <v>105</v>
       </c>
     </row>
     <row r="81">
       <c r="N81" s="0" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="O81" s="0" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
     </row>
     <row r="82">
       <c r="N82" s="0" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="O82" s="0" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
     </row>
     <row r="83">
       <c r="N83" s="0" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="O83" s="0" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="84">
       <c r="N84" s="0" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="O84" s="0" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
     </row>
     <row r="85">
       <c r="N85" s="0" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="O85" s="0" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
     </row>
     <row r="86">
       <c r="N86" s="0" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="O86" s="0" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
     </row>
     <row r="87">
       <c r="N87" s="0" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="O87" s="0" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
     </row>
     <row r="88">
       <c r="N88" s="0" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="O88" s="0" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="89">
       <c r="N89" s="0" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="O89" s="0" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="90">
       <c r="N90" s="0" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="O90" s="0" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="91">
       <c r="N91" s="0" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="O91" s="0" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
     </row>
     <row r="92">
       <c r="N92" s="0" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="O92" s="0" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
     </row>
     <row r="93">
       <c r="N93" s="0" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="O93" s="0" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
     </row>
     <row r="94">
       <c r="N94" s="0" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="O94" s="0" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
     </row>
     <row r="95">
       <c r="N95" s="0" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="O95" s="0" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
     </row>
     <row r="96">
       <c r="N96" s="0" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="O96" s="0" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
     </row>
     <row r="97">
       <c r="N97" s="0" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="O97" s="0" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="98">
       <c r="N98" s="0" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="O98" s="0" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
     </row>
     <row r="99">
       <c r="N99" s="0" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="O99" s="0" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
     </row>
     <row r="100">
       <c r="N100" s="0" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="O100" s="0" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
     </row>
     <row r="101">
       <c r="N101" s="0" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="O101" s="0" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="102">
       <c r="N102" s="0" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="O102" s="0" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
     </row>
     <row r="103">
       <c r="N103" s="0" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="O103" s="0" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
     </row>
     <row r="104">
       <c r="N104" s="0" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="O104" s="0" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
     </row>
     <row r="105">
       <c r="N105" s="0" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="O105" s="0" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
     </row>
     <row r="106">
       <c r="N106" s="0" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="O106" s="0" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
     </row>
     <row r="107">
       <c r="N107" s="0" t="s">
-        <v>130</v>
+        <v>333</v>
       </c>
       <c r="O107" s="0" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="108">
       <c r="N108" s="0" t="s">
-        <v>144</v>
+        <v>335</v>
       </c>
       <c r="O108" s="0" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
     </row>
     <row r="109">
       <c r="N109" s="0" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="O109" s="0" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
     </row>
     <row r="110">
       <c r="N110" s="0" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="O110" s="0" t="s">
-        <v>91</v>
+        <v>340</v>
       </c>
     </row>
     <row r="111">
       <c r="N111" s="0" t="s">
-        <v>331</v>
+        <v>132</v>
       </c>
       <c r="O111" s="0" t="s">
-        <v>332</v>
+        <v>91</v>
       </c>
     </row>
     <row r="112">
       <c r="N112" s="0" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="O112" s="0" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
     </row>
     <row r="113">
       <c r="N113" s="0" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="O113" s="0" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="114">
       <c r="N114" s="0" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="O114" s="0" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="115">
       <c r="N115" s="0" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="O115" s="0" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
     </row>
     <row r="116">
+      <c r="N116" s="0" t="s">
+        <v>348</v>
+      </c>
       <c r="O116" s="0" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="117">
+      <c r="N117" s="0" t="s">
+        <v>350</v>
+      </c>
       <c r="O117" s="0" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
     </row>
     <row r="118">
+      <c r="N118" s="0" t="s">
+        <v>127</v>
+      </c>
       <c r="O118" s="0" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
     </row>
     <row r="119">
+      <c r="N119" s="0" t="s">
+        <v>353</v>
+      </c>
       <c r="O119" s="0" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
     </row>
     <row r="120">
+      <c r="N120" s="0" t="s">
+        <v>355</v>
+      </c>
       <c r="O120" s="0" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
     </row>
     <row r="121">
       <c r="O121" s="0" t="s">
-        <v>142</v>
+        <v>357</v>
       </c>
     </row>
     <row r="122">
       <c r="O122" s="0" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
     </row>
     <row r="123">
       <c r="O123" s="0" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
     </row>
     <row r="124">
       <c r="O124" s="0" t="s">
-        <v>347</v>
+        <v>143</v>
       </c>
     </row>
     <row r="125">
       <c r="O125" s="0" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
     </row>
     <row r="126">
       <c r="O126" s="0" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
     </row>
     <row r="127">
       <c r="O127" s="0" t="s">
-        <v>292</v>
+        <v>362</v>
       </c>
     </row>
     <row r="128">
       <c r="O128" s="0" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
     </row>
     <row r="129">
       <c r="O129" s="0" t="s">
-        <v>130</v>
+        <v>364</v>
       </c>
     </row>
     <row r="130">
       <c r="O130" s="0" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
     </row>
     <row r="131">
       <c r="O131" s="0" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
     </row>
     <row r="132">
       <c r="O132" s="0" t="s">
-        <v>353</v>
+        <v>309</v>
       </c>
     </row>
     <row r="133">
       <c r="O133" s="0" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
     </row>
     <row r="134">
       <c r="O134" s="0" t="s">
-        <v>355</v>
+        <v>132</v>
       </c>
     </row>
     <row r="135">
       <c r="O135" s="0" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
     </row>
     <row r="136">
       <c r="O136" s="0" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
     </row>
     <row r="137">
       <c r="O137" s="0" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
     </row>
     <row r="138">
       <c r="O138" s="0" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
     </row>
     <row r="139">
       <c r="O139" s="0" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
     </row>
     <row r="140">
       <c r="O140" s="0" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
     </row>
     <row r="141">
       <c r="O141" s="0" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
     </row>
     <row r="142">
       <c r="O142" s="0" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
     </row>
     <row r="143">
       <c r="O143" s="0" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
     </row>
     <row r="144">
       <c r="O144" s="0" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
     </row>
     <row r="145">
       <c r="O145" s="0" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
     </row>
     <row r="146">
       <c r="O146" s="0" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
     </row>
     <row r="147">
       <c r="O147" s="0" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
     </row>
     <row r="148">
       <c r="O148" s="0" t="s">
-        <v>369</v>
+        <v>381</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="O149" s="0" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="O150" s="0" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="O151" s="0" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="O152" s="0" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="O153" s="0" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="O154" s="0" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="O155" s="0" t="s">
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -3740,19 +3886,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
@@ -3764,39 +3910,39 @@
         <v>2</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>33</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="F2" s="0" t="s">
         <v>54</v>
@@ -3811,13 +3957,13 @@
         <v>39</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="K2" s="0">
         <v>1</v>
       </c>
       <c r="L2" s="0" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="M2" s="0">
         <f>IF($L$2="","NEW","Live")</f>
@@ -3828,19 +3974,19 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="B3" s="0" t="s">
         <v>33</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="F3" s="0" t="s">
         <v>54</v>
@@ -3855,13 +4001,13 @@
         <v>39</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="K3" s="0">
         <v>1</v>
       </c>
       <c r="L3" s="0" t="s">
-        <v>388</v>
+        <v>407</v>
       </c>
       <c r="M3" s="0">
         <f>IF($L$3="","NEW","Live")</f>
@@ -3872,19 +4018,19 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>33</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="F4" s="0" t="s">
         <v>36</v>
@@ -3899,13 +4045,13 @@
         <v>39</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="K4" s="0">
         <v>1</v>
       </c>
       <c r="L4" s="0" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="M4" s="0">
         <f>IF($L$4="","NEW","Live")</f>
@@ -3916,19 +4062,19 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>33</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="F5" s="0" t="s">
         <v>54</v>
@@ -3943,13 +4089,13 @@
         <v>39</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="K5" s="0">
         <v>1</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>397</v>
+        <v>416</v>
       </c>
       <c r="M5" s="0">
         <f>IF($L$5="","NEW","Live")</f>
@@ -3960,19 +4106,19 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>33</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="F6" s="0" t="s">
         <v>36</v>
@@ -3987,13 +4133,13 @@
         <v>39</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K6" s="0">
         <v>1</v>
       </c>
       <c r="L6" s="0" t="s">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="M6" s="0">
         <f>IF($L$6="","NEW","Live")</f>
@@ -4004,19 +4150,19 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="F7" s="0" t="s">
         <v>54</v>
@@ -4031,13 +4177,13 @@
         <v>39</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="K7" s="0">
         <v>1</v>
       </c>
       <c r="L7" s="0" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
       <c r="M7" s="0">
         <f>IF($L$7="","NEW","Live")</f>
@@ -4048,19 +4194,19 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>406</v>
+        <v>425</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>33</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>407</v>
+        <v>426</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>408</v>
+        <v>427</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="F8" s="0" t="s">
         <v>20</v>
@@ -4075,13 +4221,13 @@
         <v>39</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="K8" s="0">
         <v>1</v>
       </c>
       <c r="L8" s="0" t="s">
-        <v>410</v>
+        <v>429</v>
       </c>
       <c r="M8" s="0">
         <f>IF($L$8="","NEW","Live")</f>
@@ -4092,19 +4238,19 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>33</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="F9" s="0" t="s">
         <v>36</v>
@@ -4125,7 +4271,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="0" t="s">
-        <v>414</v>
+        <v>433</v>
       </c>
       <c r="M9" s="0">
         <f>IF($L$9="","NEW","Live")</f>
@@ -4136,19 +4282,19 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>416</v>
+        <v>435</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="F10" s="0" t="s">
         <v>20</v>
@@ -4163,13 +4309,13 @@
         <v>39</v>
       </c>
       <c r="J10" s="0" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K10" s="0">
         <v>1</v>
       </c>
       <c r="L10" s="0" t="s">
-        <v>418</v>
+        <v>437</v>
       </c>
       <c r="M10" s="0">
         <f>IF($L$10="","NEW","Live")</f>
@@ -4180,19 +4326,19 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>419</v>
+        <v>438</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>419</v>
+        <v>438</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>420</v>
+        <v>439</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>421</v>
+        <v>440</v>
       </c>
       <c r="F11" s="0" t="s">
         <v>54</v>
@@ -4207,13 +4353,13 @@
         <v>39</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="K11" s="0">
         <v>1</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="M11" s="0">
         <f>IF($L$11="","NEW","Live")</f>
@@ -4224,19 +4370,19 @@
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>424</v>
+        <v>443</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>425</v>
+        <v>444</v>
       </c>
       <c r="F12" s="0" t="s">
         <v>54</v>
@@ -4251,13 +4397,13 @@
         <v>39</v>
       </c>
       <c r="J12" s="0" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="K12" s="0">
         <v>1</v>
       </c>
       <c r="L12" s="0" t="s">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="M12" s="0">
         <f>IF($L$12="","NEW","Live")</f>
@@ -4268,19 +4414,19 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>428</v>
+        <v>447</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>429</v>
+        <v>448</v>
       </c>
       <c r="F13" s="0" t="s">
         <v>36</v>
@@ -4295,13 +4441,13 @@
         <v>39</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K13" s="0">
         <v>1</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="M13" s="0">
         <f>IF($L$13="","NEW","Live")</f>
@@ -4312,19 +4458,19 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>433</v>
+        <v>452</v>
       </c>
       <c r="F14" s="0" t="s">
         <v>36</v>
@@ -4339,13 +4485,13 @@
         <v>39</v>
       </c>
       <c r="J14" s="0" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="K14" s="0">
         <v>1</v>
       </c>
       <c r="L14" s="0" t="s">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="M14" s="0">
         <f>IF($L$14="","NEW","Live")</f>
@@ -4356,19 +4502,19 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>435</v>
+        <v>454</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>435</v>
+        <v>454</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>437</v>
+        <v>456</v>
       </c>
       <c r="F15" s="0" t="s">
         <v>54</v>
@@ -4383,13 +4529,13 @@
         <v>39</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="K15" s="0">
         <v>1</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="M15" s="0">
         <f>IF($L$15="","NEW","Live")</f>
@@ -4400,19 +4546,19 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>439</v>
+        <v>458</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>439</v>
+        <v>458</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>441</v>
+        <v>460</v>
       </c>
       <c r="F16" s="0" t="s">
         <v>54</v>
@@ -4427,13 +4573,13 @@
         <v>39</v>
       </c>
       <c r="J16" s="0" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="K16" s="0">
         <v>1</v>
       </c>
       <c r="L16" s="0" t="s">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="M16" s="0">
         <f>IF($L$16="","NEW","Live")</f>
@@ -4444,19 +4590,19 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="B17" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>444</v>
+        <v>463</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>445</v>
+        <v>464</v>
       </c>
       <c r="F17" s="0" t="s">
         <v>68</v>
@@ -4471,13 +4617,13 @@
         <v>39</v>
       </c>
       <c r="J17" s="0" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K17" s="0">
         <v>1</v>
       </c>
       <c r="L17" s="0" t="s">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="M17" s="0">
         <f>IF($L$17="","NEW","Live")</f>
@@ -4488,19 +4634,19 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="B18" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="F18" s="0" t="s">
         <v>68</v>
@@ -4515,13 +4661,13 @@
         <v>39</v>
       </c>
       <c r="J18" s="0" t="s">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="K18" s="0">
         <v>2</v>
       </c>
       <c r="L18" s="0" t="s">
-        <v>451</v>
+        <v>470</v>
       </c>
       <c r="M18" s="0">
         <f>IF($L$18="","NEW","Live")</f>
@@ -4532,19 +4678,19 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>452</v>
+        <v>471</v>
       </c>
       <c r="B19" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>452</v>
+        <v>471</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>453</v>
+        <v>472</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="F19" s="0" t="s">
         <v>36</v>
@@ -4559,13 +4705,13 @@
         <v>39</v>
       </c>
       <c r="J19" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="K19" s="0">
         <v>1</v>
       </c>
       <c r="L19" s="0" t="s">
-        <v>454</v>
+        <v>473</v>
       </c>
       <c r="M19" s="0">
         <f>IF($L$19="","NEW","Live")</f>
@@ -4576,19 +4722,19 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="F20" s="0" t="s">
         <v>36</v>
@@ -4603,13 +4749,13 @@
         <v>39</v>
       </c>
       <c r="J20" s="0" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="K20" s="0">
         <v>1</v>
       </c>
       <c r="L20" s="0" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="M20" s="0">
         <f>IF($L$20="","NEW","Live")</f>
@@ -4620,19 +4766,19 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="B21" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="F21" s="0" t="s">
         <v>20</v>
@@ -4647,13 +4793,13 @@
         <v>39</v>
       </c>
       <c r="J21" s="0" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="K21" s="0">
         <v>1</v>
       </c>
       <c r="L21" s="0" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="M21" s="0">
         <f>IF($L$21="","NEW","Live")</f>
@@ -4664,19 +4810,19 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="B22" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="F22" s="0" t="s">
         <v>20</v>
@@ -4691,13 +4837,13 @@
         <v>39</v>
       </c>
       <c r="J22" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="K22" s="0">
         <v>1</v>
       </c>
       <c r="L22" s="0" t="s">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="M22" s="0">
         <f>IF($L$22="","NEW","Live")</f>
@@ -4708,19 +4854,19 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="B23" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>467</v>
+        <v>486</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="F23" s="0" t="s">
         <v>36</v>
@@ -4735,13 +4881,13 @@
         <v>39</v>
       </c>
       <c r="J23" s="0" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="K23" s="0">
         <v>1</v>
       </c>
       <c r="L23" s="0" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="M23" s="0">
         <f>IF($L$23="","NEW","Live")</f>
@@ -4752,19 +4898,19 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>470</v>
+        <v>489</v>
       </c>
       <c r="B24" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>470</v>
+        <v>489</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>471</v>
+        <v>490</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>472</v>
+        <v>491</v>
       </c>
       <c r="F24" s="0" t="s">
         <v>68</v>
@@ -4779,13 +4925,13 @@
         <v>39</v>
       </c>
       <c r="J24" s="0" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="K24" s="0">
         <v>1</v>
       </c>
       <c r="L24" s="0" t="s">
-        <v>473</v>
+        <v>492</v>
       </c>
       <c r="M24" s="0">
         <f>IF($L$24="","NEW","Live")</f>
@@ -4796,19 +4942,19 @@
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>475</v>
+        <v>494</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>476</v>
+        <v>495</v>
       </c>
       <c r="F25" s="0" t="s">
         <v>54</v>
@@ -4823,13 +4969,13 @@
         <v>39</v>
       </c>
       <c r="J25" s="0" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="K25" s="0">
         <v>1</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>477</v>
+        <v>496</v>
       </c>
       <c r="M25" s="0">
         <f>IF($L$25="","NEW","Live")</f>
@@ -4840,19 +4986,19 @@
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>479</v>
+        <v>498</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>480</v>
+        <v>499</v>
       </c>
       <c r="F26" s="0" t="s">
         <v>36</v>
@@ -4867,13 +5013,13 @@
         <v>39</v>
       </c>
       <c r="J26" s="0" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="K26" s="0">
         <v>1</v>
       </c>
       <c r="L26" s="0" t="s">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="M26" s="0">
         <f>IF($L$26="","NEW","Live")</f>
@@ -4884,19 +5030,19 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>482</v>
+        <v>501</v>
       </c>
       <c r="B27" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>482</v>
+        <v>501</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>483</v>
+        <v>502</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>484</v>
+        <v>503</v>
       </c>
       <c r="F27" s="0" t="s">
         <v>54</v>
@@ -4911,13 +5057,13 @@
         <v>39</v>
       </c>
       <c r="J27" s="0" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="K27" s="0">
         <v>1</v>
       </c>
       <c r="L27" s="0" t="s">
-        <v>485</v>
+        <v>504</v>
       </c>
       <c r="M27" s="0">
         <f>IF($L$27="","NEW","Live")</f>
@@ -4928,19 +5074,19 @@
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>486</v>
+        <v>505</v>
       </c>
       <c r="B28" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>486</v>
+        <v>505</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="F28" s="0" t="s">
         <v>68</v>
@@ -4955,13 +5101,13 @@
         <v>39</v>
       </c>
       <c r="J28" s="0" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
       <c r="K28" s="0">
         <v>2</v>
       </c>
       <c r="L28" s="0" t="s">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="M28" s="0">
         <f>IF($L$28="","NEW","Live")</f>
@@ -4972,19 +5118,19 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>491</v>
+        <v>510</v>
       </c>
       <c r="B29" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>491</v>
+        <v>510</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>493</v>
+        <v>512</v>
       </c>
       <c r="F29" s="0" t="s">
         <v>36</v>
@@ -4999,13 +5145,13 @@
         <v>39</v>
       </c>
       <c r="J29" s="0" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="K29" s="0">
         <v>1</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="M29" s="0">
         <f>IF($L$29="","NEW","Live")</f>
@@ -5016,19 +5162,19 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="B30" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>496</v>
+        <v>515</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="F30" s="0" t="s">
         <v>36</v>
@@ -5049,7 +5195,7 @@
         <v>1</v>
       </c>
       <c r="L30" s="0" t="s">
-        <v>498</v>
+        <v>517</v>
       </c>
       <c r="M30" s="0">
         <f>IF($L$30="","NEW","Live")</f>
@@ -5060,19 +5206,19 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="B31" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>500</v>
+        <v>519</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>501</v>
+        <v>520</v>
       </c>
       <c r="F31" s="0" t="s">
         <v>54</v>
@@ -5087,13 +5233,13 @@
         <v>39</v>
       </c>
       <c r="J31" s="0" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K31" s="0">
         <v>1</v>
       </c>
       <c r="L31" s="0" t="s">
-        <v>502</v>
+        <v>521</v>
       </c>
       <c r="M31" s="0">
         <f>IF($L$31="","NEW","Live")</f>
@@ -5104,19 +5250,19 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="B32" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>504</v>
+        <v>523</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>505</v>
+        <v>524</v>
       </c>
       <c r="F32" s="0" t="s">
         <v>54</v>
@@ -5131,13 +5277,13 @@
         <v>39</v>
       </c>
       <c r="J32" s="0" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="K32" s="0">
         <v>1</v>
       </c>
       <c r="L32" s="0" t="s">
-        <v>506</v>
+        <v>525</v>
       </c>
       <c r="M32" s="0">
         <f>IF($L$32="","NEW","Live")</f>
@@ -5148,19 +5294,19 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>507</v>
+        <v>526</v>
       </c>
       <c r="B33" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>507</v>
+        <v>526</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>508</v>
+        <v>527</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>509</v>
+        <v>528</v>
       </c>
       <c r="F33" s="0" t="s">
         <v>20</v>
@@ -5175,13 +5321,13 @@
         <v>39</v>
       </c>
       <c r="J33" s="0" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="K33" s="0">
         <v>1</v>
       </c>
       <c r="L33" s="0" t="s">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="M33" s="0">
         <f>IF($L$33="","NEW","Live")</f>
@@ -5192,19 +5338,19 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="B34" s="0" t="s">
         <v>51</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="F34" s="0" t="s">
         <v>36</v>
@@ -5219,13 +5365,13 @@
         <v>39</v>
       </c>
       <c r="J34" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="K34" s="0">
         <v>1</v>
       </c>
       <c r="L34" s="0" t="s">
-        <v>513</v>
+        <v>532</v>
       </c>
       <c r="M34" s="0">
         <f>IF($L$34="","NEW","Live")</f>
@@ -6090,90 +6236,90 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>514</v>
+        <v>533</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>518</v>
+        <v>537</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>520</v>
+        <v>539</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>523</v>
+        <v>542</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>524</v>
+        <v>543</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>525</v>
+        <v>544</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>526</v>
+        <v>545</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>527</v>
+        <v>546</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>528</v>
+        <v>547</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>529</v>
+        <v>548</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>530</v>
+        <v>549</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>531</v>
+        <v>550</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>532</v>
+        <v>551</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>533</v>
+        <v>552</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>534</v>
+        <v>553</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="B2" s="0">
         <v>0</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="E2" s="0" t="s">
         <v>33</v>
@@ -6224,10 +6370,10 @@
         <v>33</v>
       </c>
       <c r="U2" s="0" t="s">
-        <v>535</v>
+        <v>554</v>
       </c>
       <c r="V2" s="0" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="W2" s="0">
         <f>IF($V$2="","NEW","Live")</f>
@@ -6238,16 +6384,16 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="B3" s="0">
         <v>0</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="E3" s="0" t="s">
         <v>33</v>
@@ -6265,10 +6411,10 @@
         <v>33</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>33</v>
+        <v>227</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="L3" s="0" t="s">
         <v>33</v>
@@ -6298,10 +6444,10 @@
         <v>33</v>
       </c>
       <c r="U3" s="0" t="s">
-        <v>536</v>
+        <v>555</v>
       </c>
       <c r="V3" s="0" t="s">
-        <v>388</v>
+        <v>407</v>
       </c>
       <c r="W3" s="0">
         <f>IF($V$3="","NEW","Live")</f>
@@ -6312,22 +6458,22 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="B4" s="0">
         <v>0</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>33</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="G4" s="0" t="s">
         <v>33</v>
@@ -6372,10 +6518,10 @@
         <v>33</v>
       </c>
       <c r="U4" s="0" t="s">
-        <v>538</v>
+        <v>557</v>
       </c>
       <c r="V4" s="0" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="W4" s="0">
         <f>IF($V$4="","NEW","Live")</f>
@@ -6386,16 +6532,16 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="B5" s="0">
         <v>0</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>33</v>
@@ -6446,10 +6592,10 @@
         <v>33</v>
       </c>
       <c r="U5" s="0" t="s">
-        <v>539</v>
+        <v>558</v>
       </c>
       <c r="V5" s="0" t="s">
-        <v>397</v>
+        <v>416</v>
       </c>
       <c r="W5" s="0">
         <f>IF($V$5="","NEW","Live")</f>
@@ -6460,16 +6606,16 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="B6" s="0">
         <v>0</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>33</v>
@@ -6499,10 +6645,10 @@
         <v>33</v>
       </c>
       <c r="N6" s="0" t="s">
-        <v>540</v>
+        <v>559</v>
       </c>
       <c r="O6" s="0" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="P6" s="0" t="s">
         <v>33</v>
@@ -6520,10 +6666,10 @@
         <v>33</v>
       </c>
       <c r="U6" s="0" t="s">
-        <v>541</v>
+        <v>560</v>
       </c>
       <c r="V6" s="0" t="s">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="W6" s="0">
         <f>IF($V$6="","NEW","Live")</f>
@@ -6534,22 +6680,22 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="B7" s="0">
         <v>0</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>33</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>542</v>
+        <v>561</v>
       </c>
       <c r="G7" s="0" t="s">
         <v>33</v>
@@ -6594,10 +6740,10 @@
         <v>33</v>
       </c>
       <c r="U7" s="0" t="s">
-        <v>543</v>
+        <v>562</v>
       </c>
       <c r="V7" s="0" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
       <c r="W7" s="0">
         <f>IF($V$7="","NEW","Live")</f>
@@ -6608,22 +6754,22 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>406</v>
+        <v>425</v>
       </c>
       <c r="B8" s="0">
         <v>0</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="E8" s="0" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>544</v>
+        <v>563</v>
       </c>
       <c r="G8" s="0" t="s">
         <v>33</v>
@@ -6668,10 +6814,10 @@
         <v>33</v>
       </c>
       <c r="U8" s="0" t="s">
-        <v>545</v>
+        <v>564</v>
       </c>
       <c r="V8" s="0" t="s">
-        <v>410</v>
+        <v>429</v>
       </c>
       <c r="W8" s="0">
         <f>IF($V$8="","NEW","Live")</f>
@@ -6682,7 +6828,7 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="B9" s="0">
         <v>0</v>
@@ -6691,13 +6837,13 @@
         <v>29</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>33</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="G9" s="0" t="s">
         <v>33</v>
@@ -6742,10 +6888,10 @@
         <v>33</v>
       </c>
       <c r="U9" s="0" t="s">
-        <v>546</v>
+        <v>565</v>
       </c>
       <c r="V9" s="0" t="s">
-        <v>414</v>
+        <v>433</v>
       </c>
       <c r="W9" s="0">
         <f>IF($V$9="","NEW","Live")</f>
@@ -6756,16 +6902,16 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="B10" s="0">
         <v>0</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="E10" s="0" t="s">
         <v>33</v>
@@ -6795,10 +6941,10 @@
         <v>33</v>
       </c>
       <c r="N10" s="0" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="O10" s="0" t="s">
-        <v>540</v>
+        <v>559</v>
       </c>
       <c r="P10" s="0" t="s">
         <v>33</v>
@@ -6816,10 +6962,10 @@
         <v>33</v>
       </c>
       <c r="U10" s="0" t="s">
-        <v>547</v>
+        <v>566</v>
       </c>
       <c r="V10" s="0" t="s">
-        <v>418</v>
+        <v>437</v>
       </c>
       <c r="W10" s="0">
         <f>IF($V$10="","NEW","Live")</f>
@@ -6830,16 +6976,16 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>419</v>
+        <v>438</v>
       </c>
       <c r="B11" s="0">
         <v>0</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>421</v>
+        <v>440</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>33</v>
@@ -6848,10 +6994,10 @@
         <v>33</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>540</v>
+        <v>559</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="I11" s="0" t="s">
         <v>33</v>
@@ -6890,10 +7036,10 @@
         <v>33</v>
       </c>
       <c r="U11" s="0" t="s">
-        <v>548</v>
+        <v>567</v>
       </c>
       <c r="V11" s="0" t="s">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="W11" s="0">
         <f>IF($V$11="","NEW","Live")</f>
@@ -6904,22 +7050,22 @@
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="B12" s="0">
         <v>0</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>425</v>
+        <v>444</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>33</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>549</v>
+        <v>568</v>
       </c>
       <c r="G12" s="0" t="s">
         <v>33</v>
@@ -6964,10 +7110,10 @@
         <v>33</v>
       </c>
       <c r="U12" s="0" t="s">
-        <v>550</v>
+        <v>569</v>
       </c>
       <c r="V12" s="0" t="s">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="W12" s="0">
         <f>IF($V$12="","NEW","Live")</f>
@@ -6978,19 +7124,19 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="B13" s="0">
         <v>0</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>429</v>
+        <v>448</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>544</v>
+        <v>563</v>
       </c>
       <c r="F13" s="0" t="s">
         <v>33</v>
@@ -7038,10 +7184,10 @@
         <v>33</v>
       </c>
       <c r="U13" s="0" t="s">
-        <v>551</v>
+        <v>570</v>
       </c>
       <c r="V13" s="0" t="s">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="W13" s="0">
         <f>IF($V$13="","NEW","Live")</f>
@@ -7052,22 +7198,22 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="B14" s="0">
         <v>0</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>433</v>
+        <v>452</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>33</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="G14" s="0" t="s">
         <v>33</v>
@@ -7112,10 +7258,10 @@
         <v>33</v>
       </c>
       <c r="U14" s="0" t="s">
-        <v>552</v>
+        <v>571</v>
       </c>
       <c r="V14" s="0" t="s">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="W14" s="0">
         <f>IF($V$14="","NEW","Live")</f>
@@ -7126,16 +7272,16 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>435</v>
+        <v>454</v>
       </c>
       <c r="B15" s="0">
         <v>0</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>437</v>
+        <v>456</v>
       </c>
       <c r="E15" s="0" t="s">
         <v>33</v>
@@ -7186,10 +7332,10 @@
         <v>33</v>
       </c>
       <c r="U15" s="0" t="s">
-        <v>553</v>
+        <v>572</v>
       </c>
       <c r="V15" s="0" t="s">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="W15" s="0">
         <f>IF($V$15="","NEW","Live")</f>
@@ -7200,16 +7346,16 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>439</v>
+        <v>458</v>
       </c>
       <c r="B16" s="0">
         <v>0</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>441</v>
+        <v>460</v>
       </c>
       <c r="E16" s="0" t="s">
         <v>33</v>
@@ -7218,7 +7364,7 @@
         <v>33</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="H16" s="0" t="s">
         <v>33</v>
@@ -7233,7 +7379,7 @@
         <v>33</v>
       </c>
       <c r="L16" s="0" t="s">
-        <v>540</v>
+        <v>559</v>
       </c>
       <c r="M16" s="0" t="s">
         <v>24</v>
@@ -7260,10 +7406,10 @@
         <v>33</v>
       </c>
       <c r="U16" s="0" t="s">
-        <v>554</v>
+        <v>573</v>
       </c>
       <c r="V16" s="0" t="s">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="W16" s="0">
         <f>IF($V$16="","NEW","Live")</f>
@@ -7274,16 +7420,16 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="B17" s="0">
         <v>0</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>445</v>
+        <v>464</v>
       </c>
       <c r="E17" s="0" t="s">
         <v>33</v>
@@ -7313,10 +7459,10 @@
         <v>33</v>
       </c>
       <c r="N17" s="0" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="O17" s="0" t="s">
-        <v>544</v>
+        <v>563</v>
       </c>
       <c r="P17" s="0" t="s">
         <v>33</v>
@@ -7334,10 +7480,10 @@
         <v>33</v>
       </c>
       <c r="U17" s="0" t="s">
-        <v>555</v>
+        <v>574</v>
       </c>
       <c r="V17" s="0" t="s">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="W17" s="0">
         <f>IF($V$17="","NEW","Live")</f>
@@ -7348,7 +7494,7 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="B18" s="0">
         <v>0</v>
@@ -7357,13 +7503,13 @@
         <v>29</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="E18" s="0" t="s">
         <v>33</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>544</v>
+        <v>563</v>
       </c>
       <c r="G18" s="0" t="s">
         <v>33</v>
@@ -7408,10 +7554,10 @@
         <v>33</v>
       </c>
       <c r="U18" s="0" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
       <c r="V18" s="0" t="s">
-        <v>451</v>
+        <v>470</v>
       </c>
       <c r="W18" s="0">
         <f>IF($V$18="","NEW","Live")</f>
@@ -7422,16 +7568,16 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="B19" s="0">
         <v>1</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="E19" s="0" t="s">
         <v>33</v>
@@ -7440,7 +7586,7 @@
         <v>33</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>540</v>
+        <v>559</v>
       </c>
       <c r="H19" s="0" t="s">
         <v>33</v>
@@ -7455,7 +7601,7 @@
         <v>33</v>
       </c>
       <c r="L19" s="0" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="M19" s="0" t="s">
         <v>40</v>
@@ -7482,10 +7628,10 @@
         <v>33</v>
       </c>
       <c r="U19" s="0" t="s">
-        <v>557</v>
+        <v>576</v>
       </c>
       <c r="V19" s="0" t="s">
-        <v>451</v>
+        <v>470</v>
       </c>
       <c r="W19" s="0">
         <f>IF($V$19="","NEW","Live")</f>
@@ -7496,16 +7642,16 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>452</v>
+        <v>471</v>
       </c>
       <c r="B20" s="0">
         <v>0</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="E20" s="0" t="s">
         <v>33</v>
@@ -7556,10 +7702,10 @@
         <v>33</v>
       </c>
       <c r="U20" s="0" t="s">
-        <v>558</v>
+        <v>577</v>
       </c>
       <c r="V20" s="0" t="s">
-        <v>454</v>
+        <v>473</v>
       </c>
       <c r="W20" s="0">
         <f>IF($V$20="","NEW","Live")</f>
@@ -7570,16 +7716,16 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="B21" s="0">
         <v>0</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="E21" s="0" t="s">
         <v>33</v>
@@ -7618,7 +7764,7 @@
         <v>33</v>
       </c>
       <c r="Q21" s="0" t="s">
-        <v>544</v>
+        <v>563</v>
       </c>
       <c r="R21" s="0" t="s">
         <v>33</v>
@@ -7630,10 +7776,10 @@
         <v>91</v>
       </c>
       <c r="U21" s="0" t="s">
-        <v>559</v>
+        <v>578</v>
       </c>
       <c r="V21" s="0" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="W21" s="0">
         <f>IF($V$21="","NEW","Live")</f>
@@ -7644,22 +7790,22 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="B22" s="0">
         <v>0</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="E22" s="0" t="s">
         <v>33</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="G22" s="0" t="s">
         <v>33</v>
@@ -7704,10 +7850,10 @@
         <v>33</v>
       </c>
       <c r="U22" s="0" t="s">
-        <v>560</v>
+        <v>579</v>
       </c>
       <c r="V22" s="0" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="W22" s="0">
         <f>IF($V$22="","NEW","Live")</f>
@@ -7718,16 +7864,16 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="B23" s="0">
         <v>0</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="E23" s="0" t="s">
         <v>33</v>
@@ -7778,10 +7924,10 @@
         <v>33</v>
       </c>
       <c r="U23" s="0" t="s">
-        <v>561</v>
+        <v>580</v>
       </c>
       <c r="V23" s="0" t="s">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="W23" s="0">
         <f>IF($V$23="","NEW","Live")</f>
@@ -7792,16 +7938,16 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="B24" s="0">
         <v>0</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="E24" s="0" t="s">
         <v>33</v>
@@ -7840,7 +7986,7 @@
         <v>33</v>
       </c>
       <c r="Q24" s="0" t="s">
-        <v>544</v>
+        <v>563</v>
       </c>
       <c r="R24" s="0" t="s">
         <v>33</v>
@@ -7849,13 +7995,13 @@
         <v>33</v>
       </c>
       <c r="T24" s="0" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="U24" s="0" t="s">
-        <v>562</v>
+        <v>581</v>
       </c>
       <c r="V24" s="0" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="W24" s="0">
         <f>IF($V$24="","NEW","Live")</f>
@@ -7866,16 +8012,16 @@
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>470</v>
+        <v>489</v>
       </c>
       <c r="B25" s="0">
         <v>0</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>472</v>
+        <v>491</v>
       </c>
       <c r="E25" s="0" t="s">
         <v>33</v>
@@ -7884,10 +8030,10 @@
         <v>33</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="I25" s="0" t="s">
         <v>33</v>
@@ -7926,10 +8072,10 @@
         <v>33</v>
       </c>
       <c r="U25" s="0" t="s">
-        <v>563</v>
+        <v>582</v>
       </c>
       <c r="V25" s="0" t="s">
-        <v>473</v>
+        <v>492</v>
       </c>
       <c r="W25" s="0">
         <f>IF($V$25="","NEW","Live")</f>
@@ -7940,22 +8086,22 @@
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="B26" s="0">
         <v>0</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>476</v>
+        <v>495</v>
       </c>
       <c r="E26" s="0" t="s">
         <v>33</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>549</v>
+        <v>568</v>
       </c>
       <c r="G26" s="0" t="s">
         <v>33</v>
@@ -8000,10 +8146,10 @@
         <v>33</v>
       </c>
       <c r="U26" s="0" t="s">
-        <v>564</v>
+        <v>583</v>
       </c>
       <c r="V26" s="0" t="s">
-        <v>477</v>
+        <v>496</v>
       </c>
       <c r="W26" s="0">
         <f>IF($V$26="","NEW","Live")</f>
@@ -8014,16 +8160,16 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="B27" s="0">
         <v>0</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>480</v>
+        <v>499</v>
       </c>
       <c r="E27" s="0" t="s">
         <v>33</v>
@@ -8062,7 +8208,7 @@
         <v>33</v>
       </c>
       <c r="Q27" s="0" t="s">
-        <v>544</v>
+        <v>563</v>
       </c>
       <c r="R27" s="0" t="s">
         <v>33</v>
@@ -8074,10 +8220,10 @@
         <v>98</v>
       </c>
       <c r="U27" s="0" t="s">
-        <v>565</v>
+        <v>584</v>
       </c>
       <c r="V27" s="0" t="s">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="W27" s="0">
         <f>IF($V$27="","NEW","Live")</f>
@@ -8088,16 +8234,16 @@
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>482</v>
+        <v>501</v>
       </c>
       <c r="B28" s="0">
         <v>0</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>484</v>
+        <v>503</v>
       </c>
       <c r="E28" s="0" t="s">
         <v>33</v>
@@ -8106,10 +8252,10 @@
         <v>33</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>540</v>
+        <v>559</v>
       </c>
       <c r="I28" s="0" t="s">
         <v>33</v>
@@ -8148,10 +8294,10 @@
         <v>33</v>
       </c>
       <c r="U28" s="0" t="s">
-        <v>566</v>
+        <v>585</v>
       </c>
       <c r="V28" s="0" t="s">
-        <v>485</v>
+        <v>504</v>
       </c>
       <c r="W28" s="0">
         <f>IF($V$28="","NEW","Live")</f>
@@ -8162,16 +8308,16 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>486</v>
+        <v>505</v>
       </c>
       <c r="B29" s="0">
         <v>0</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="E29" s="0" t="s">
         <v>33</v>
@@ -8210,7 +8356,7 @@
         <v>33</v>
       </c>
       <c r="Q29" s="0" t="s">
-        <v>549</v>
+        <v>568</v>
       </c>
       <c r="R29" s="0" t="s">
         <v>33</v>
@@ -8222,10 +8368,10 @@
         <v>91</v>
       </c>
       <c r="U29" s="0" t="s">
-        <v>567</v>
+        <v>586</v>
       </c>
       <c r="V29" s="0" t="s">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="W29" s="0">
         <f>IF($V$29="","NEW","Live")</f>
@@ -8236,22 +8382,22 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>486</v>
+        <v>505</v>
       </c>
       <c r="B30" s="0">
         <v>1</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="E30" s="0" t="s">
         <v>33</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="G30" s="0" t="s">
         <v>33</v>
@@ -8296,10 +8442,10 @@
         <v>33</v>
       </c>
       <c r="U30" s="0" t="s">
-        <v>568</v>
+        <v>587</v>
       </c>
       <c r="V30" s="0" t="s">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="W30" s="0">
         <f>IF($V$30="","NEW","Live")</f>
@@ -8310,16 +8456,16 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>491</v>
+        <v>510</v>
       </c>
       <c r="B31" s="0">
         <v>0</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>493</v>
+        <v>512</v>
       </c>
       <c r="E31" s="0" t="s">
         <v>33</v>
@@ -8358,7 +8504,7 @@
         <v>33</v>
       </c>
       <c r="Q31" s="0" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="R31" s="0" t="s">
         <v>33</v>
@@ -8367,13 +8513,13 @@
         <v>33</v>
       </c>
       <c r="T31" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="U31" s="0" t="s">
-        <v>569</v>
+        <v>588</v>
       </c>
       <c r="V31" s="0" t="s">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="W31" s="0">
         <f>IF($V$31="","NEW","Live")</f>
@@ -8384,7 +8530,7 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="B32" s="0">
         <v>0</v>
@@ -8393,13 +8539,13 @@
         <v>29</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="E32" s="0" t="s">
         <v>33</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="G32" s="0" t="s">
         <v>33</v>
@@ -8435,7 +8581,7 @@
         <v>33</v>
       </c>
       <c r="R32" s="0" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="S32" s="0" t="s">
         <v>33</v>
@@ -8444,10 +8590,10 @@
         <v>33</v>
       </c>
       <c r="U32" s="0" t="s">
-        <v>570</v>
+        <v>589</v>
       </c>
       <c r="V32" s="0" t="s">
-        <v>498</v>
+        <v>517</v>
       </c>
       <c r="W32" s="0">
         <f>IF($V$32="","NEW","Live")</f>
@@ -8458,16 +8604,16 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="B33" s="0">
         <v>0</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>501</v>
+        <v>520</v>
       </c>
       <c r="E33" s="0" t="s">
         <v>33</v>
@@ -8503,7 +8649,7 @@
         <v>33</v>
       </c>
       <c r="P33" s="0" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="Q33" s="0" t="s">
         <v>33</v>
@@ -8518,10 +8664,10 @@
         <v>33</v>
       </c>
       <c r="U33" s="0" t="s">
-        <v>571</v>
+        <v>590</v>
       </c>
       <c r="V33" s="0" t="s">
-        <v>502</v>
+        <v>521</v>
       </c>
       <c r="W33" s="0">
         <f>IF($V$33="","NEW","Live")</f>
@@ -8532,16 +8678,16 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="B34" s="0">
         <v>0</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>505</v>
+        <v>524</v>
       </c>
       <c r="E34" s="0" t="s">
         <v>33</v>
@@ -8580,7 +8726,7 @@
         <v>33</v>
       </c>
       <c r="Q34" s="0" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="R34" s="0" t="s">
         <v>33</v>
@@ -8589,13 +8735,13 @@
         <v>33</v>
       </c>
       <c r="T34" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="U34" s="0" t="s">
-        <v>572</v>
+        <v>591</v>
       </c>
       <c r="V34" s="0" t="s">
-        <v>506</v>
+        <v>525</v>
       </c>
       <c r="W34" s="0">
         <f>IF($V$34="","NEW","Live")</f>
@@ -8606,22 +8752,22 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>507</v>
+        <v>526</v>
       </c>
       <c r="B35" s="0">
         <v>0</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>509</v>
+        <v>528</v>
       </c>
       <c r="E35" s="0" t="s">
         <v>33</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="G35" s="0" t="s">
         <v>33</v>
@@ -8666,10 +8812,10 @@
         <v>33</v>
       </c>
       <c r="U35" s="0" t="s">
-        <v>573</v>
+        <v>592</v>
       </c>
       <c r="V35" s="0" t="s">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="W35" s="0">
         <f>IF($V$35="","NEW","Live")</f>
@@ -8680,16 +8826,16 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="B36" s="0">
         <v>0</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="E36" s="0" t="s">
         <v>33</v>
@@ -8740,10 +8886,10 @@
         <v>33</v>
       </c>
       <c r="U36" s="0" t="s">
-        <v>574</v>
+        <v>593</v>
       </c>
       <c r="V36" s="0" t="s">
-        <v>513</v>
+        <v>532</v>
       </c>
       <c r="W36" s="0">
         <f>IF($V$36="","NEW","Live")</f>
@@ -9365,7 +9511,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK208"/>
+  <dimension ref="A1:AM208"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -9380,8 +9526,8 @@
     <col min="10" max="10" width="14" customWidth="1" outlineLevel="1"/>
     <col min="11" max="11" width="14" customWidth="1" outlineLevel="1"/>
     <col min="12" max="12" width="14" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="14" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1" outlineLevel="1"/>
     <col min="16" max="16" width="14" customWidth="1" outlineLevel="1"/>
     <col min="17" max="17" width="14" customWidth="1" outlineLevel="1"/>
@@ -9390,13 +9536,13 @@
     <col min="20" max="20" width="14" customWidth="1" outlineLevel="1"/>
     <col min="21" max="21" width="14" customWidth="1" outlineLevel="1"/>
     <col min="22" max="22" width="14" customWidth="1" outlineLevel="1"/>
-    <col min="23" max="23" width="14" customWidth="1"/>
-    <col min="24" max="24" width="14" customWidth="1"/>
-    <col min="25" max="25" width="14" customWidth="1" outlineLevel="1"/>
-    <col min="26" max="26" width="14" customWidth="1" outlineLevel="1"/>
+    <col min="23" max="23" width="14" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="24" width="14" customWidth="1" outlineLevel="1"/>
+    <col min="25" max="25" width="14" customWidth="1"/>
+    <col min="26" max="26" width="14" customWidth="1"/>
     <col min="27" max="27" width="14" customWidth="1" outlineLevel="1"/>
-    <col min="28" max="28" width="14" customWidth="1"/>
-    <col min="29" max="29" width="14" customWidth="1"/>
+    <col min="28" max="28" width="14" customWidth="1" outlineLevel="1"/>
+    <col min="29" max="29" width="14" customWidth="1" outlineLevel="1"/>
     <col min="30" max="30" width="14" customWidth="1"/>
     <col min="31" max="31" width="14" customWidth="1"/>
     <col min="32" max="32" width="14" customWidth="1"/>
@@ -9405,124 +9551,132 @@
     <col min="35" max="35" width="14" customWidth="1"/>
     <col min="36" max="36" width="14" customWidth="1"/>
     <col min="37" max="37" width="14" customWidth="1"/>
+    <col min="38" max="38" width="14" customWidth="1"/>
+    <col min="39" max="39" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>514</v>
+        <v>533</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>575</v>
+        <v>594</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>576</v>
+        <v>595</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>577</v>
+        <v>596</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>578</v>
+        <v>597</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>579</v>
+        <v>598</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>580</v>
+        <v>599</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>581</v>
+        <v>600</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>582</v>
+        <v>601</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>583</v>
+        <v>602</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>584</v>
+        <v>603</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>586</v>
+        <v>605</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>587</v>
+        <v>606</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>588</v>
+        <v>607</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>589</v>
+        <v>608</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>590</v>
+        <v>609</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>591</v>
+        <v>610</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>592</v>
+        <v>611</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>593</v>
+        <v>612</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>594</v>
+        <v>613</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>595</v>
+        <v>614</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>596</v>
+        <v>615</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>597</v>
+        <v>616</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>598</v>
+        <v>617</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>599</v>
+        <v>618</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>600</v>
+        <v>619</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>601</v>
+        <v>620</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>602</v>
+        <v>621</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>603</v>
+        <v>622</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>604</v>
+        <v>623</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>534</v>
+        <v>624</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>378</v>
+        <v>625</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>379</v>
+        <v>553</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>380</v>
+        <v>397</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="B2" s="0">
         <v>0</v>
@@ -9558,10 +9712,10 @@
         <v>33</v>
       </c>
       <c r="M2" s="0" t="s">
-        <v>605</v>
+        <v>33</v>
       </c>
       <c r="N2" s="0" t="s">
-        <v>33</v>
+        <v>626</v>
       </c>
       <c r="O2" s="0" t="s">
         <v>33</v>
@@ -9618,24 +9772,30 @@
         <v>33</v>
       </c>
       <c r="AG2" s="0" t="s">
-        <v>606</v>
+        <v>33</v>
       </c>
       <c r="AH2" s="0" t="s">
-        <v>535</v>
+        <v>33</v>
       </c>
       <c r="AI2" s="0" t="s">
-        <v>384</v>
-      </c>
-      <c r="AJ2" s="0">
-        <f>IF($AI$2="","NEW","Live")</f>
+        <v>627</v>
+      </c>
+      <c r="AJ2" s="0" t="s">
+        <v>554</v>
       </c>
       <c r="AK2" s="0" t="s">
+        <v>403</v>
+      </c>
+      <c r="AL2" s="0">
+        <f>IF($AK$2="","NEW","Live")</f>
+      </c>
+      <c r="AM2" s="0" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="B3" s="0">
         <v>0</v>
@@ -9662,17 +9822,17 @@
         <v>33</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>540</v>
+        <v>559</v>
       </c>
       <c r="L3" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="M3" s="0" t="s">
-        <v>33</v>
-      </c>
       <c r="N3" s="0" t="s">
         <v>33</v>
       </c>
@@ -9707,16 +9867,16 @@
         <v>33</v>
       </c>
       <c r="Y3" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z3" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA3" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="Z3" s="0" t="s">
-        <v>540</v>
-      </c>
-      <c r="AA3" s="0" t="s">
-        <v>33</v>
-      </c>
       <c r="AB3" s="0" t="s">
-        <v>33</v>
+        <v>559</v>
       </c>
       <c r="AC3" s="0" t="s">
         <v>33</v>
@@ -9731,24 +9891,30 @@
         <v>33</v>
       </c>
       <c r="AG3" s="0" t="s">
-        <v>607</v>
+        <v>33</v>
       </c>
       <c r="AH3" s="0" t="s">
-        <v>536</v>
+        <v>33</v>
       </c>
       <c r="AI3" s="0" t="s">
-        <v>388</v>
-      </c>
-      <c r="AJ3" s="0">
-        <f>IF($AI$3="","NEW","Live")</f>
+        <v>628</v>
+      </c>
+      <c r="AJ3" s="0" t="s">
+        <v>555</v>
       </c>
       <c r="AK3" s="0" t="s">
+        <v>407</v>
+      </c>
+      <c r="AL3" s="0">
+        <f>IF($AK$3="","NEW","Live")</f>
+      </c>
+      <c r="AM3" s="0" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="B4" s="0">
         <v>0</v>
@@ -9814,54 +9980,60 @@
         <v>33</v>
       </c>
       <c r="W4" s="0" t="s">
-        <v>537</v>
+        <v>33</v>
       </c>
       <c r="X4" s="0" t="s">
-        <v>540</v>
+        <v>33</v>
       </c>
       <c r="Y4" s="0" t="s">
-        <v>33</v>
+        <v>556</v>
       </c>
       <c r="Z4" s="0" t="s">
-        <v>33</v>
+        <v>559</v>
       </c>
       <c r="AA4" s="0" t="s">
         <v>33</v>
       </c>
       <c r="AB4" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC4" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD4" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="AC4" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD4" s="0" t="s">
-        <v>33</v>
-      </c>
       <c r="AE4" s="0" t="s">
         <v>33</v>
       </c>
       <c r="AF4" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG4" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH4" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="AG4" s="0" t="s">
-        <v>608</v>
-      </c>
-      <c r="AH4" s="0" t="s">
-        <v>539</v>
-      </c>
       <c r="AI4" s="0" t="s">
-        <v>397</v>
-      </c>
-      <c r="AJ4" s="0">
-        <f>IF($AI$4="","NEW","Live")</f>
+        <v>629</v>
+      </c>
+      <c r="AJ4" s="0" t="s">
+        <v>558</v>
       </c>
       <c r="AK4" s="0" t="s">
+        <v>416</v>
+      </c>
+      <c r="AL4" s="0">
+        <f>IF($AK$4="","NEW","Live")</f>
+      </c>
+      <c r="AM4" s="0" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>435</v>
+        <v>454</v>
       </c>
       <c r="B5" s="0">
         <v>0</v>
@@ -9897,10 +10069,10 @@
         <v>33</v>
       </c>
       <c r="M5" s="0" t="s">
-        <v>549</v>
+        <v>33</v>
       </c>
       <c r="N5" s="0" t="s">
-        <v>33</v>
+        <v>568</v>
       </c>
       <c r="O5" s="0" t="s">
         <v>33</v>
@@ -9933,48 +10105,54 @@
         <v>33</v>
       </c>
       <c r="Y5" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z5" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA5" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="Z5" s="0" t="s">
-        <v>540</v>
-      </c>
-      <c r="AA5" s="0" t="s">
-        <v>33</v>
-      </c>
       <c r="AB5" s="0" t="s">
-        <v>33</v>
+        <v>559</v>
       </c>
       <c r="AC5" s="0" t="s">
-        <v>540</v>
+        <v>33</v>
       </c>
       <c r="AD5" s="0" t="s">
         <v>33</v>
       </c>
       <c r="AE5" s="0" t="s">
-        <v>33</v>
+        <v>559</v>
       </c>
       <c r="AF5" s="0" t="s">
         <v>33</v>
       </c>
       <c r="AG5" s="0" t="s">
-        <v>609</v>
+        <v>33</v>
       </c>
       <c r="AH5" s="0" t="s">
-        <v>553</v>
+        <v>33</v>
       </c>
       <c r="AI5" s="0" t="s">
-        <v>438</v>
-      </c>
-      <c r="AJ5" s="0">
-        <f>IF($AI$5="","NEW","Live")</f>
+        <v>630</v>
+      </c>
+      <c r="AJ5" s="0" t="s">
+        <v>572</v>
       </c>
       <c r="AK5" s="0" t="s">
+        <v>457</v>
+      </c>
+      <c r="AL5" s="0">
+        <f>IF($AK$5="","NEW","Live")</f>
+      </c>
+      <c r="AM5" s="0" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>452</v>
+        <v>471</v>
       </c>
       <c r="B6" s="0">
         <v>0</v>
@@ -10010,10 +10188,10 @@
         <v>33</v>
       </c>
       <c r="M6" s="0" t="s">
-        <v>605</v>
+        <v>33</v>
       </c>
       <c r="N6" s="0" t="s">
-        <v>33</v>
+        <v>626</v>
       </c>
       <c r="O6" s="0" t="s">
         <v>33</v>
@@ -10070,24 +10248,30 @@
         <v>33</v>
       </c>
       <c r="AG6" s="0" t="s">
-        <v>610</v>
+        <v>33</v>
       </c>
       <c r="AH6" s="0" t="s">
-        <v>558</v>
+        <v>33</v>
       </c>
       <c r="AI6" s="0" t="s">
-        <v>454</v>
-      </c>
-      <c r="AJ6" s="0">
-        <f>IF($AI$6="","NEW","Live")</f>
+        <v>631</v>
+      </c>
+      <c r="AJ6" s="0" t="s">
+        <v>577</v>
       </c>
       <c r="AK6" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="AL6" s="0">
+        <f>IF($AK$6="","NEW","Live")</f>
+      </c>
+      <c r="AM6" s="0" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="B7" s="0">
         <v>0</v>
@@ -10123,10 +10307,10 @@
         <v>33</v>
       </c>
       <c r="M7" s="0" t="s">
-        <v>605</v>
+        <v>33</v>
       </c>
       <c r="N7" s="0" t="s">
-        <v>33</v>
+        <v>626</v>
       </c>
       <c r="O7" s="0" t="s">
         <v>33</v>
@@ -10183,24 +10367,30 @@
         <v>33</v>
       </c>
       <c r="AG7" s="0" t="s">
-        <v>611</v>
+        <v>33</v>
       </c>
       <c r="AH7" s="0" t="s">
-        <v>561</v>
+        <v>33</v>
       </c>
       <c r="AI7" s="0" t="s">
-        <v>465</v>
-      </c>
-      <c r="AJ7" s="0">
-        <f>IF($AI$7="","NEW","Live")</f>
+        <v>632</v>
+      </c>
+      <c r="AJ7" s="0" t="s">
+        <v>580</v>
       </c>
       <c r="AK7" s="0" t="s">
+        <v>484</v>
+      </c>
+      <c r="AL7" s="0">
+        <f>IF($AK$7="","NEW","Live")</f>
+      </c>
+      <c r="AM7" s="0" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="B8" s="0">
         <v>0</v>
@@ -10266,48 +10456,54 @@
         <v>33</v>
       </c>
       <c r="W8" s="0" t="s">
-        <v>537</v>
+        <v>33</v>
       </c>
       <c r="X8" s="0" t="s">
-        <v>540</v>
+        <v>33</v>
       </c>
       <c r="Y8" s="0" t="s">
-        <v>33</v>
+        <v>556</v>
       </c>
       <c r="Z8" s="0" t="s">
-        <v>33</v>
+        <v>559</v>
       </c>
       <c r="AA8" s="0" t="s">
         <v>33</v>
       </c>
       <c r="AB8" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC8" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD8" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="AC8" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD8" s="0" t="s">
-        <v>33</v>
-      </c>
       <c r="AE8" s="0" t="s">
         <v>33</v>
       </c>
       <c r="AF8" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG8" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH8" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="AG8" s="0" t="s">
-        <v>612</v>
-      </c>
-      <c r="AH8" s="0" t="s">
-        <v>574</v>
-      </c>
       <c r="AI8" s="0" t="s">
-        <v>513</v>
-      </c>
-      <c r="AJ8" s="0">
-        <f>IF($AI$8="","NEW","Live")</f>
+        <v>633</v>
+      </c>
+      <c r="AJ8" s="0" t="s">
+        <v>593</v>
       </c>
       <c r="AK8" s="0" t="s">
+        <v>532</v>
+      </c>
+      <c r="AL8" s="0">
+        <f>IF($AK$8="","NEW","Live")</f>
+      </c>
+      <c r="AM8" s="0" t="s">
         <v>33</v>
       </c>
     </row>
@@ -10912,7 +11108,7 @@
       <c r="E208" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK8"/>
+  <autoFilter ref="A1:AM8"/>
   <dataValidations count="1">
     <dataValidation type="list" sqref="D2:D208" showErrorMessage="0" allowBlank="1">
       <formula1>=list_CardModType</formula1>
@@ -10934,16 +11130,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -10958,7 +11154,7 @@
         <v>17</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>613</v>
+        <v>634</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>45</v>
@@ -10967,7 +11163,7 @@
         <v>18</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -11004,10 +11200,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -11019,36 +11215,36 @@
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>614</v>
+        <v>635</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>615</v>
+        <v>636</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>616</v>
+        <v>637</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>617</v>
+        <v>638</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>618</v>
+        <v>639</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>619</v>
+        <v>640</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>54</v>
@@ -11063,10 +11259,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="I2" s="0" t="s">
         <v>34</v>
@@ -11086,10 +11282,10 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>54</v>
@@ -11104,19 +11300,19 @@
         <v>1</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="I3" s="0" t="s">
         <v>34</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>33</v>
+        <v>227</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="L3" s="0" t="s">
         <v>39</v>
@@ -11127,10 +11323,10 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>36</v>
@@ -11145,13 +11341,13 @@
         <v>1</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="H4" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J4" s="0" t="s">
         <v>33</v>
@@ -11168,10 +11364,10 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>54</v>
@@ -11186,10 +11382,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="I5" s="0" t="s">
         <v>34</v>
@@ -11204,15 +11400,15 @@
         <v>39</v>
       </c>
       <c r="M5" s="0" t="s">
-        <v>621</v>
+        <v>642</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="C6" s="0" t="s">
         <v>36</v>
@@ -11227,13 +11423,13 @@
         <v>1</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="H6" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J6" s="0" t="s">
         <v>33</v>
@@ -11250,10 +11446,10 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>54</v>
@@ -11268,13 +11464,13 @@
         <v>1</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H7" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J7" s="0" t="s">
         <v>33</v>
@@ -11286,15 +11482,15 @@
         <v>39</v>
       </c>
       <c r="M7" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>406</v>
+        <v>425</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>407</v>
+        <v>426</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>20</v>
@@ -11309,13 +11505,13 @@
         <v>1</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="H8" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J8" s="0" t="s">
         <v>33</v>
@@ -11327,15 +11523,15 @@
         <v>39</v>
       </c>
       <c r="M8" s="0" t="s">
-        <v>623</v>
+        <v>644</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>36</v>
@@ -11356,7 +11552,7 @@
         <v>34</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J9" s="0" t="s">
         <v>33</v>
@@ -11368,15 +11564,15 @@
         <v>39</v>
       </c>
       <c r="M9" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>20</v>
@@ -11391,13 +11587,13 @@
         <v>1</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="H10" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J10" s="0" t="s">
         <v>33</v>
@@ -11409,15 +11605,15 @@
         <v>39</v>
       </c>
       <c r="M10" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>419</v>
+        <v>438</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>419</v>
+        <v>438</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>54</v>
@@ -11432,13 +11628,13 @@
         <v>1</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="H11" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J11" s="0" t="s">
         <v>33</v>
@@ -11450,15 +11646,15 @@
         <v>39</v>
       </c>
       <c r="M11" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>54</v>
@@ -11473,13 +11669,13 @@
         <v>1</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="H12" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J12" s="0" t="s">
         <v>33</v>
@@ -11491,15 +11687,15 @@
         <v>39</v>
       </c>
       <c r="M12" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>36</v>
@@ -11514,13 +11710,13 @@
         <v>1</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H13" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J13" s="0" t="s">
         <v>33</v>
@@ -11532,15 +11728,15 @@
         <v>39</v>
       </c>
       <c r="M13" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>36</v>
@@ -11555,13 +11751,13 @@
         <v>1</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="H14" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J14" s="0" t="s">
         <v>33</v>
@@ -11573,15 +11769,15 @@
         <v>39</v>
       </c>
       <c r="M14" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>435</v>
+        <v>454</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>435</v>
+        <v>454</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>54</v>
@@ -11596,10 +11792,10 @@
         <v>1</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="I15" s="0" t="s">
         <v>34</v>
@@ -11614,15 +11810,15 @@
         <v>39</v>
       </c>
       <c r="M15" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>439</v>
+        <v>458</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>439</v>
+        <v>458</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>54</v>
@@ -11637,13 +11833,13 @@
         <v>1</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="H16" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J16" s="0" t="s">
         <v>33</v>
@@ -11655,15 +11851,15 @@
         <v>39</v>
       </c>
       <c r="M16" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>68</v>
@@ -11678,13 +11874,13 @@
         <v>1</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="H17" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J17" s="0" t="s">
         <v>33</v>
@@ -11696,15 +11892,15 @@
         <v>39</v>
       </c>
       <c r="M17" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>68</v>
@@ -11719,13 +11915,13 @@
         <v>2</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="H18" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J18" s="0" t="s">
         <v>33</v>
@@ -11737,15 +11933,15 @@
         <v>39</v>
       </c>
       <c r="M18" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>452</v>
+        <v>471</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>452</v>
+        <v>471</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>36</v>
@@ -11760,10 +11956,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="I19" s="0" t="s">
         <v>34</v>
@@ -11778,15 +11974,15 @@
         <v>39</v>
       </c>
       <c r="M19" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>36</v>
@@ -11801,13 +11997,13 @@
         <v>1</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="H20" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J20" s="0" t="s">
         <v>33</v>
@@ -11819,15 +12015,15 @@
         <v>39</v>
       </c>
       <c r="M20" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>20</v>
@@ -11842,13 +12038,13 @@
         <v>1</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="H21" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J21" s="0" t="s">
         <v>33</v>
@@ -11860,15 +12056,15 @@
         <v>39</v>
       </c>
       <c r="M21" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>20</v>
@@ -11883,10 +12079,10 @@
         <v>1</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="I22" s="0" t="s">
         <v>34</v>
@@ -11901,15 +12097,15 @@
         <v>39</v>
       </c>
       <c r="M22" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>36</v>
@@ -11924,13 +12120,13 @@
         <v>1</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="H23" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J23" s="0" t="s">
         <v>33</v>
@@ -11942,15 +12138,15 @@
         <v>39</v>
       </c>
       <c r="M23" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>470</v>
+        <v>489</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>470</v>
+        <v>489</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>68</v>
@@ -11965,13 +12161,13 @@
         <v>1</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="H24" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J24" s="0" t="s">
         <v>33</v>
@@ -11983,15 +12179,15 @@
         <v>39</v>
       </c>
       <c r="M24" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>54</v>
@@ -12006,13 +12202,13 @@
         <v>1</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="H25" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J25" s="0" t="s">
         <v>33</v>
@@ -12024,15 +12220,15 @@
         <v>39</v>
       </c>
       <c r="M25" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>36</v>
@@ -12047,13 +12243,13 @@
         <v>1</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="H26" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J26" s="0" t="s">
         <v>33</v>
@@ -12065,15 +12261,15 @@
         <v>39</v>
       </c>
       <c r="M26" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>482</v>
+        <v>501</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>482</v>
+        <v>501</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>54</v>
@@ -12088,13 +12284,13 @@
         <v>1</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="H27" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J27" s="0" t="s">
         <v>33</v>
@@ -12106,15 +12302,15 @@
         <v>39</v>
       </c>
       <c r="M27" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>486</v>
+        <v>505</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>486</v>
+        <v>505</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>68</v>
@@ -12129,13 +12325,13 @@
         <v>2</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
       <c r="H28" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J28" s="0" t="s">
         <v>33</v>
@@ -12147,15 +12343,15 @@
         <v>39</v>
       </c>
       <c r="M28" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>491</v>
+        <v>510</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>491</v>
+        <v>510</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>36</v>
@@ -12170,13 +12366,13 @@
         <v>1</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="H29" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J29" s="0" t="s">
         <v>33</v>
@@ -12188,15 +12384,15 @@
         <v>39</v>
       </c>
       <c r="M29" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>36</v>
@@ -12217,7 +12413,7 @@
         <v>34</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J30" s="0" t="s">
         <v>33</v>
@@ -12229,15 +12425,15 @@
         <v>39</v>
       </c>
       <c r="M30" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>54</v>
@@ -12252,13 +12448,13 @@
         <v>1</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H31" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J31" s="0" t="s">
         <v>33</v>
@@ -12270,15 +12466,15 @@
         <v>39</v>
       </c>
       <c r="M31" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>54</v>
@@ -12293,13 +12489,13 @@
         <v>1</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="H32" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J32" s="0" t="s">
         <v>33</v>
@@ -12311,15 +12507,15 @@
         <v>39</v>
       </c>
       <c r="M32" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>507</v>
+        <v>526</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>507</v>
+        <v>526</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>20</v>
@@ -12334,13 +12530,13 @@
         <v>1</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="H33" s="0" t="s">
         <v>34</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="J33" s="0" t="s">
         <v>33</v>
@@ -12352,15 +12548,15 @@
         <v>39</v>
       </c>
       <c r="M33" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>36</v>
@@ -12375,10 +12571,10 @@
         <v>1</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="I34" s="0" t="s">
         <v>34</v>
@@ -12393,7 +12589,7 @@
         <v>39</v>
       </c>
       <c r="M34" s="0" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
   </sheetData>
@@ -12409,7 +12605,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -12418,7 +12614,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>624</v>
+        <v>645</v>
       </c>
     </row>
     <row r="2">
@@ -12428,7 +12624,7 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>625</v>
+        <v>646</v>
       </c>
     </row>
     <row r="4">
@@ -12438,55 +12634,55 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>626</v>
+        <v>647</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>628</v>
+        <v>649</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>629</v>
+        <v>650</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>630</v>
+        <v>651</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>631</v>
+        <v>652</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>632</v>
+        <v>653</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>633</v>
+        <v>654</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>634</v>
+        <v>655</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>635</v>
+        <v>656</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>636</v>
+        <v>657</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>637</v>
+        <v>658</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>638</v>
+        <v>659</v>
       </c>
     </row>
     <row r="12">
@@ -12496,39 +12692,39 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>639</v>
+        <v>660</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>640</v>
+        <v>661</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>641</v>
+        <v>662</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>642</v>
+        <v>663</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>643</v>
+        <v>664</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>644</v>
+        <v>665</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>645</v>
+        <v>666</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>646</v>
+        <v>667</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>647</v>
+        <v>668</v>
       </c>
     </row>
     <row r="18">
@@ -12538,7 +12734,7 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
-        <v>648</v>
+        <v>669</v>
       </c>
     </row>
     <row r="20">
@@ -12548,18 +12744,18 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>649</v>
+        <v>670</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>650</v>
+        <v>671</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>651</v>
+        <v>672</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="23">
@@ -12569,18 +12765,18 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>652</v>
+        <v>674</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="26">
@@ -12590,18 +12786,18 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>655</v>
+        <v>675</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>651</v>
+        <v>676</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="29">
@@ -12611,18 +12807,18 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>656</v>
+        <v>677</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>657</v>
+        <v>672</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="32">
@@ -12632,18 +12828,18 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>649</v>
+        <v>678</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>651</v>
+        <v>679</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="35">
@@ -12653,47 +12849,47 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>659</v>
+        <v>672</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="0" t="s">
-        <v>660</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>652</v>
+      <c r="A38" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="s">
-        <v>100</v>
+      <c r="A39" s="0" t="s">
+        <v>680</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>673</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>658</v>
+        <v>681</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>661</v>
+        <v>682</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="42">
@@ -12703,18 +12899,18 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>649</v>
+        <v>680</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>662</v>
+        <v>683</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="45">
@@ -12724,18 +12920,18 @@
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>664</v>
+        <v>684</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="48">
@@ -12745,18 +12941,18 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>651</v>
+        <v>685</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>665</v>
+        <v>686</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
     </row>
     <row r="51">
@@ -12766,346 +12962,383 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="s">
-        <v>30</v>
+      <c r="A53" s="0" t="s">
+        <v>687</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>688</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="0" t="s">
-        <v>668</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>652</v>
+      <c r="A54" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>669</v>
+        <v>689</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="0" t="s">
-        <v>671</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>652</v>
+      <c r="A56" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>672</v>
+        <v>690</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>673</v>
+        <v>691</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>674</v>
+        <v>692</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
-        <v>677</v>
+        <v>694</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>680</v>
+        <v>696</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
-        <v>681</v>
+        <v>697</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>682</v>
+        <v>698</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="s">
-        <v>48</v>
+      <c r="A63" s="0" t="s">
+        <v>699</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>700</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
-        <v>683</v>
+        <v>701</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>684</v>
+        <v>702</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
-        <v>685</v>
+        <v>703</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>686</v>
+        <v>704</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="s">
-        <v>687</v>
+        <v>705</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>688</v>
+        <v>706</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="0" t="s">
-        <v>689</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>652</v>
+      <c r="A67" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
-        <v>690</v>
+        <v>707</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>652</v>
+        <v>708</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
-        <v>691</v>
+        <v>709</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>674</v>
+        <v>710</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
-        <v>692</v>
+        <v>711</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>676</v>
+        <v>712</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0" t="s">
-        <v>693</v>
+        <v>713</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="s">
-        <v>63</v>
+      <c r="A72" s="0" t="s">
+        <v>714</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>673</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
-        <v>694</v>
+        <v>715</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>652</v>
+        <v>696</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="s">
-        <v>76</v>
+      <c r="A74" s="0" t="s">
+        <v>716</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>698</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
-        <v>683</v>
+        <v>717</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>684</v>
+        <v>700</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="s">
-        <v>685</v>
+        <v>718</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>686</v>
+        <v>702</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="0" t="s">
-        <v>687</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>688</v>
+      <c r="A77" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
-        <v>695</v>
+        <v>719</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
-        <v>696</v>
+        <v>707</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>652</v>
+        <v>708</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
-        <v>697</v>
+        <v>709</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>652</v>
+        <v>710</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
-        <v>698</v>
+        <v>711</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>652</v>
+        <v>712</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="s">
-        <v>94</v>
+      <c r="A83" s="0" t="s">
+        <v>720</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>673</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="0" t="s">
-        <v>683</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>684</v>
+      <c r="A84" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
-        <v>685</v>
+        <v>721</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>686</v>
+        <v>673</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
-        <v>687</v>
+        <v>722</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>688</v>
+        <v>673</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="s">
-        <v>694</v>
+        <v>723</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="0" t="s">
-        <v>699</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>652</v>
+      <c r="A88" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="s">
-        <v>101</v>
+      <c r="A89" s="0" t="s">
+        <v>707</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="s">
-        <v>700</v>
+        <v>709</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>652</v>
+        <v>710</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
-        <v>701</v>
+        <v>711</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>652</v>
+        <v>712</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
-        <v>702</v>
+        <v>719</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>703</v>
+        <v>673</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
-        <v>704</v>
+        <v>724</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
-        <v>683</v>
+        <v>725</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>684</v>
+        <v>673</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="s">
-        <v>685</v>
+        <v>726</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>686</v>
+        <v>673</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
-        <v>687</v>
+        <v>727</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>688</v>
+        <v>728</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="s">
+        <v>729</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="s">
+        <v>707</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="s">
+        <v>709</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0" t="s">
+        <v>711</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>712</v>
       </c>
     </row>
   </sheetData>
